--- a/outputs/excel/copernicus_marine.xlsx
+++ b/outputs/excel/copernicus_marine.xlsx
@@ -564,7 +564,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>['2020-11-01T00:00:00.000Z', '2026-09-22T00:00:00.000Z']</t>
+          <t>['2020-11-01T00:00:00.000Z', '2026-09-29T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -640,7 +640,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>['2022-11-01T03:00:00.000Z', '2026-09-22T00:00:00.000Z']</t>
+          <t>['2022-11-01T03:00:00.000Z', '2026-09-29T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>['2021-10-01T00:00:00.000Z', '2026-09-21T00:00:00.000Z']</t>
+          <t>['2021-10-01T00:00:00.000Z', '2026-09-28T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>['2021-07-05T00:00:00.000Z', '2026-09-21T23:00:00.000Z']</t>
+          <t>['2021-07-05T00:00:00.000Z', '2026-09-28T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>['2022-08-01T00:00:00.000Z', '2026-09-16T12:00:00.000Z']</t>
+          <t>['2022-08-01T00:00:00.000Z', '2026-09-20T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1346,7 +1346,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>['2019-01-01T00:00:00.000Z', '2026-09-21T00:00:00.000Z']</t>
+          <t>['2019-01-01T00:00:00.000Z', '2026-09-28T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>['2019-08-01T00:00:00.000Z', '2026-09-19T23:00:00.000Z']</t>
+          <t>['2019-08-01T00:00:00.000Z', '2026-09-26T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-09-21T23:45:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-09-28T23:45:00.000Z']</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>['1991-01-01T00:00:00.000Z', '2026-05-31T00:00:00.000Z']</t>
+          <t>['1991-01-01T00:00:00.000Z', '2026-06-30T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1664,7 +1664,7 @@
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>['2021-11-01T00:00:00.000Z', '2026-09-21T12:00:00.000Z']</t>
+          <t>['2021-11-01T00:00:00.000Z', '2026-09-28T12:00:00.000Z']</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>['2021-10-01T01:00:00.000Z', '2026-09-21T12:00:00.000Z']</t>
+          <t>['2021-10-01T01:00:00.000Z', '2026-09-28T12:00:00.000Z']</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2050,7 +2050,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>['2022-11-01T00:00:00.000Z', '2026-09-20T00:00:00.000Z']</t>
+          <t>['2022-11-01T00:00:00.000Z', '2026-09-27T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>['1980-01-01T01:00:00.000Z', '2026-06-01T00:00:00.000Z']</t>
+          <t>['1980-01-01T01:00:00.000Z', '2026-07-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>['2021-11-01T00:00:00.000Z', '2026-09-21T00:00:00.000Z']</t>
+          <t>['2021-11-01T00:00:00.000Z', '2026-09-28T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2436,7 +2436,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>['2022-12-18T00:00:00.000Z', '2026-09-22T11:00:00.000Z']</t>
+          <t>['2022-12-18T00:00:00.000Z', '2026-09-29T11:00:00.000Z']</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>['2023-10-01T00:00:00.000Z', '2026-09-21T23:00:00.000Z']</t>
+          <t>['2023-10-01T00:00:00.000Z', '2026-09-28T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-07-01T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-08-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>['1992-01-01T00:00:00.000Z', '2026-06-01T00:00:00.000Z']</t>
+          <t>['1992-01-01T00:00:00.000Z', '2026-08-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>['2022-11-22T00:00:00.000Z', '2026-09-22T00:00:00.000Z']</t>
+          <t>['2022-11-22T00:00:00.000Z', '2026-09-29T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2900,7 +2900,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>['2022-11-26T00:00:00.000Z', '2026-09-21T23:00:00.000Z']</t>
+          <t>['2022-11-26T00:00:00.000Z', '2026-09-28T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2978,7 +2978,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>['2022-11-23T00:00:00.000Z', '2026-09-19T00:00:00.000Z']</t>
+          <t>['2022-11-23T00:00:00.000Z', '2026-09-26T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3132,7 +3132,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>['1980-01-01T00:00:00.000Z', '2026-04-28T23:00:00.000Z']</t>
+          <t>['1980-01-01T00:00:00.000Z', '2026-05-30T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -3288,7 +3288,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>['2023-11-01T00:00:00.000Z', '2026-09-21T23:00:00.000Z']</t>
+          <t>['2023-11-01T00:00:00.000Z', '2026-09-28T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -3364,7 +3364,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>['2021-11-30T00:00:00.000Z', '2026-09-22T11:00:00.000Z']</t>
+          <t>['2021-11-30T00:00:00.000Z', '2026-09-29T11:00:00.000Z']</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -3442,7 +3442,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>['2023-10-01T00:00:00.000Z', '2026-09-21T00:00:00.000Z']</t>
+          <t>['2023-10-01T00:00:00.000Z', '2026-09-28T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -3596,7 +3596,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>['1985-01-01T00:00:00.000Z', '2026-07-31T23:00:00.000Z']</t>
+          <t>['1985-01-01T00:00:00.000Z', '2026-08-31T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>['2024-08-02T00:00:00.000Z', '2026-09-19T00:00:00.000Z']</t>
+          <t>['2024-08-02T00:00:00.000Z', '2026-09-26T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3828,7 +3828,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>['2024-07-29T00:00:00.000Z', '2026-09-18T00:00:00.000Z']</t>
+          <t>['2024-07-29T00:00:00.000Z', '2026-09-25T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>['2024-08-06T00:00:00.000Z', '2026-09-18T23:00:00.000Z']</t>
+          <t>['2024-08-06T00:00:00.000Z', '2026-09-25T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3982,7 +3982,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>['2024-07-29T00:00:00.000Z', '2026-09-18T00:00:00.000Z']</t>
+          <t>['2024-07-29T00:00:00.000Z', '2026-09-25T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -4290,7 +4290,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>['2022-05-03T00:00:00.000Z', '2026-09-12T16:24:42.000Z']</t>
+          <t>['2022-05-03T00:00:00.000Z', '2026-09-19T16:03:06.770Z']</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>['2022-10-04T00:00:00.000Z', '2026-09-13T00:00:00.000Z']</t>
+          <t>['2022-10-04T00:00:00.000Z', '2026-09-20T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -4662,7 +4662,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>['2022-03-14T01:03:00.000Z', '2026-09-12T13:13:06.860Z']</t>
+          <t>['2022-03-14T01:03:00.000Z', '2026-09-19T12:55:22.151Z']</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -4738,7 +4738,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>['2022-10-04T00:00:00.000Z', '2026-09-13T00:00:00.000Z']</t>
+          <t>['2022-10-04T00:00:00.000Z', '2026-09-20T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -5338,7 +5338,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>['2026-08-26T00:00:00.000Z', '2026-09-11T00:00:00.000Z']</t>
+          <t>['2026-08-26T00:00:00.000Z', '2026-09-18T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -5414,7 +5414,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>['2023-04-01T00:00:00.000Z', '2026-09-11T00:00:00.000Z']</t>
+          <t>['2023-04-01T00:00:00.000Z', '2026-09-18T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -5794,7 +5794,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>['2026-08-25T00:00:00.000Z', '2026-09-11T00:00:00.000Z']</t>
+          <t>['2026-08-31T00:00:00.000Z', '2026-09-18T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -5870,7 +5870,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>['2026-06-01T00:00:00.000Z', '2026-09-11T00:00:00.000Z']</t>
+          <t>['2026-06-01T00:00:00.000Z', '2026-09-18T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -5946,7 +5946,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-09-11T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-09-18T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -6098,7 +6098,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>['2026-09-03T00:00:00.000Z', '2026-09-11T00:00:00.000Z']</t>
+          <t>['2026-09-04T00:00:00.000Z', '2026-09-18T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-09-11T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-09-18T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -6402,7 +6402,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>['2026-08-29T00:00:00.000Z', '2026-09-11T00:00:00.000Z']</t>
+          <t>['2026-09-04T00:00:00.000Z', '2026-09-18T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -6478,7 +6478,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>['2025-12-01T00:00:00.000Z', '2026-09-11T00:00:00.000Z']</t>
+          <t>['2025-12-01T00:00:00.000Z', '2026-09-18T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -6554,7 +6554,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-09-11T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-09-18T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -6706,7 +6706,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-09-11T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-09-18T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -6858,7 +6858,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>['2026-09-04T00:00:00.000Z', '2026-09-11T00:00:00.000Z']</t>
+          <t>['2026-09-04T00:00:00.000Z', '2026-09-18T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -6934,7 +6934,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>['2022-01-01T00:00:00.000Z', '2026-09-11T00:00:00.000Z']</t>
+          <t>['2022-01-01T00:00:00.000Z', '2026-09-18T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -7010,7 +7010,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-09-11T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-09-18T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -7314,7 +7314,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-09-05T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-09-12T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -7390,7 +7390,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-09-04T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-09-11T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -7466,7 +7466,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-09-04T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-09-11T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -7618,7 +7618,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-09-04T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-09-11T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -7694,7 +7694,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-09-04T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-09-11T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -7770,7 +7770,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-09-04T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-09-11T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -7922,7 +7922,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>['1997-09-16T00:00:00.000Z', '2026-09-04T00:00:00.000Z']</t>
+          <t>['1997-09-16T00:00:00.000Z', '2026-09-11T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -7998,7 +7998,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-08-31T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-09-07T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
@@ -8074,7 +8074,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>['1997-09-16T00:00:00.000Z', '2026-09-04T00:00:00.000Z']</t>
+          <t>['1997-09-16T00:00:00.000Z', '2026-09-11T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
@@ -8150,7 +8150,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-08-31T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-09-07T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
@@ -8226,7 +8226,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>['2026-01-01T00:00:00.000Z', '2026-09-11T00:00:00.000Z']</t>
+          <t>['2026-01-01T00:00:00.000Z', '2026-09-18T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
@@ -8302,7 +8302,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>['2020-12-20T00:00:00.000Z', '2026-09-11T00:00:00.000Z']</t>
+          <t>['2020-12-20T00:00:00.000Z', '2026-09-18T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
@@ -8378,7 +8378,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>['2024-01-17T00:00:00.000Z', '2026-09-11T00:00:00.000Z']</t>
+          <t>['2024-01-17T00:00:00.000Z', '2026-09-18T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
@@ -8454,7 +8454,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>['2020-12-20T00:00:00.000Z', '2026-09-11T00:00:00.000Z']</t>
+          <t>['2020-12-20T00:00:00.000Z', '2026-09-18T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
@@ -8530,7 +8530,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-09-10T00:00:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-09-18T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
@@ -8606,7 +8606,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>['2019-03-11T00:00:00.000Z', '2026-09-11T00:00:00.000Z']</t>
+          <t>['2019-03-11T00:00:00.000Z', '2026-09-19T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
@@ -8682,7 +8682,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>['2024-06-19T00:00:00.000Z', '2026-09-11T00:00:00.000Z']</t>
+          <t>['2024-06-19T00:00:00.000Z', '2026-09-19T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
@@ -8758,7 +8758,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>['2022-05-01T00:00:00.000Z', '2026-09-10T23:00:00.000Z']</t>
+          <t>['2022-05-01T00:00:00.000Z', '2026-09-18T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-09-12T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-09-19T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
@@ -8910,7 +8910,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-09-12T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-09-19T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
@@ -8986,7 +8986,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-09-11T23:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-09-18T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
@@ -9062,7 +9062,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-09-12T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-09-19T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
@@ -9138,7 +9138,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-09-12T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-09-19T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
@@ -9214,7 +9214,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>['2019-01-01T00:00:00.000Z', '2026-09-11T23:00:00.000Z']</t>
+          <t>['2019-01-01T00:00:00.000Z', '2026-09-18T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
@@ -9830,7 +9830,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-08-13T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-08-20T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
@@ -9906,7 +9906,7 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-08-13T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-08-20T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
@@ -9982,7 +9982,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-08-13T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-08-20T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
@@ -10058,7 +10058,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-08-13T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-08-20T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
@@ -10134,7 +10134,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>['2022-01-01T00:00:00.000Z', '2026-09-11T00:00:00.000Z']</t>
+          <t>['2022-01-01T00:00:00.000Z', '2026-09-18T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
@@ -10210,7 +10210,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>['2023-10-18T00:00:00.000Z', '2026-09-07T00:00:00.000Z']</t>
+          <t>['2023-10-18T00:00:00.000Z', '2026-09-14T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
@@ -10286,7 +10286,7 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>['2022-01-02T00:00:00.000Z', '2026-09-12T12:00:00.000Z']</t>
+          <t>['2022-01-02T00:00:00.000Z', '2026-09-19T12:00:00.000Z']</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
@@ -10362,7 +10362,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>['2023-02-02T00:00:00.000Z', '2026-09-11T00:00:00.000Z']</t>
+          <t>['2023-02-02T00:00:00.000Z', '2026-09-18T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
@@ -10438,7 +10438,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>['2025-11-01T00:00:00.000Z', '2026-09-10T00:00:00.000Z']</t>
+          <t>['2025-11-01T00:00:00.000Z', '2026-09-18T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
@@ -10514,7 +10514,7 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-09-10T00:00:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-09-18T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
@@ -10590,7 +10590,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>['2020-09-01T12:10:00.000Z', '2026-09-11T15:00:00.000Z']</t>
+          <t>['2020-09-01T12:10:00.000Z', '2026-09-18T21:10:00.000Z']</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
@@ -10666,7 +10666,7 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>['2023-11-25T06:40:00.000Z', '2026-09-13T00:19:38.000Z']</t>
+          <t>['2023-11-25T06:40:00.000Z', '2026-09-19T23:40:11.000Z']</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
@@ -10742,7 +10742,7 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-09-12T00:00:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-09-19T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
@@ -10894,7 +10894,7 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>['1978-10-25T12:00:00.000Z', '2026-08-27T00:00:00.000Z']</t>
+          <t>['1978-10-25T12:00:00.000Z', '2026-09-03T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
@@ -11434,7 +11434,7 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>['2014-10-03T20:11:44.000Z', '2026-09-11T23:39:44.000Z']</t>
+          <t>['2014-10-03T20:11:44.000Z', '2026-09-18T22:43:01.000Z']</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
@@ -11510,7 +11510,7 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>['2014-10-03T00:00:00.000Z', '2026-09-11T00:00:00.000Z']</t>
+          <t>['2014-10-03T00:00:00.000Z', '2026-09-18T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
@@ -11742,7 +11742,7 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>['2016-01-01T00:00:00.000Z', '2026-09-11T00:00:00.000Z']</t>
+          <t>['2016-01-01T00:00:00.000Z', '2026-09-18T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
@@ -11814,7 +11814,7 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>['2024-06-13T04:00:00.000Z', '2026-09-11T23:00:00.000Z']</t>
+          <t>['2024-06-13T04:00:00.000Z', '2026-09-18T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
@@ -11890,7 +11890,7 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>['2024-04-01T00:00:00.000Z', '2026-09-12T00:00:00.000Z']</t>
+          <t>['2024-04-01T00:00:00.000Z', '2026-09-19T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
@@ -11966,7 +11966,7 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>['2024-06-27T00:00:00.000Z', '2026-09-12T00:00:00.000Z']</t>
+          <t>['2024-06-27T00:00:00.000Z', '2026-09-19T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
@@ -12042,7 +12042,7 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>['2024-06-27T00:00:00.000Z', '2026-09-12T00:00:00.000Z']</t>
+          <t>['2024-06-27T00:00:00.000Z', '2026-09-19T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
@@ -12118,7 +12118,7 @@
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>['2024-06-27T00:00:00.000Z', '2026-09-12T00:00:00.000Z']</t>
+          <t>['2024-06-27T00:00:00.000Z', '2026-09-19T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
@@ -12194,7 +12194,7 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>['2024-06-27T00:00:00.000Z', '2026-09-12T00:00:00.000Z']</t>
+          <t>['2024-06-27T00:00:00.000Z', '2026-09-19T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
@@ -12270,7 +12270,7 @@
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>['1991-08-01T00:00:00.000Z', '2026-04-30T00:00:00.000Z']</t>
+          <t>['1991-08-01T00:00:00.000Z', '2026-05-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M155" t="inlineStr">
@@ -12346,7 +12346,7 @@
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>['1994-06-01T00:00:00.000Z', '2026-04-20T23:00:00.000Z']</t>
+          <t>['1994-06-01T00:00:00.000Z', '2026-05-21T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M156" t="inlineStr">
@@ -12422,7 +12422,7 @@
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>['1994-07-01T00:00:00.000Z', '2026-04-01T00:00:00.000Z']</t>
+          <t>['1994-07-01T00:00:00.000Z', '2026-05-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M157" t="inlineStr">
@@ -12898,7 +12898,7 @@
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>['2023-11-21T00:00:00.000Z', '2026-09-12T23:02:45.000Z']</t>
+          <t>['2023-11-21T00:00:00.000Z', '2026-09-19T23:01:15.000Z']</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
@@ -12974,7 +12974,7 @@
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>['2021-01-01T00:00:00.000Z', '2026-09-11T18:00:00.000Z']</t>
+          <t>['2021-01-01T00:00:00.000Z', '2026-09-18T18:00:00.000Z']</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
@@ -13122,7 +13122,7 @@
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>['2021-11-01T00:00:00.000Z', '2026-09-23T21:00:00.000Z']</t>
+          <t>['2021-11-01T00:00:00.000Z', '2026-09-30T21:00:00.000Z']</t>
         </is>
       </c>
       <c r="M166" t="inlineStr">
@@ -13580,7 +13580,7 @@
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>['1986-06-02T09:00:00.000Z', '2026-09-12T07:27:11.000Z']</t>
+          <t>['1986-06-02T09:00:00.000Z', '2026-09-19T07:13:07.000Z']</t>
         </is>
       </c>
       <c r="M172" t="inlineStr">
@@ -13647,12 +13647,12 @@
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>[-180, -90, 179.99989318847656, 90]</t>
+          <t>[-180, -90, 179.99998474121094, 90]</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-09-12T23:30:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-09-19T23:30:00.000Z']</t>
         </is>
       </c>
       <c r="M173" t="inlineStr">
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="O173" t="n">
-        <v>758</v>
+        <v>839</v>
       </c>
       <c r="P173" t="inlineStr">
         <is>
@@ -14254,7 +14254,7 @@
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>['1841-03-21T00:00:00.000Z', '2026-09-12T23:20:00.000Z']</t>
+          <t>['1841-03-21T00:00:00.000Z', '2026-09-19T23:20:00.000Z']</t>
         </is>
       </c>
       <c r="M181" t="inlineStr">
@@ -14326,7 +14326,7 @@
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>['1860-05-24T07:00:00.000Z', '2026-09-12T22:27:00.000Z']</t>
+          <t>['1860-05-24T07:00:00.000Z', '2026-09-19T22:19:00.000Z']</t>
         </is>
       </c>
       <c r="M182" t="inlineStr">
@@ -14398,7 +14398,7 @@
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>['1841-03-21T00:00:00.000Z', '2026-09-12T18:39:00.000Z']</t>
+          <t>['1841-03-21T00:00:00.000Z', '2026-09-19T18:44:00.000Z']</t>
         </is>
       </c>
       <c r="M183" t="inlineStr">
@@ -14470,7 +14470,7 @@
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-09-12T23:14:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-09-20T00:13:00.000Z']</t>
         </is>
       </c>
       <c r="M184" t="inlineStr">
@@ -14542,7 +14542,7 @@
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-09-12T21:13:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-09-19T21:13:00.000Z']</t>
         </is>
       </c>
       <c r="M185" t="inlineStr">
@@ -14614,7 +14614,7 @@
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-09-12T23:20:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-09-19T23:20:00.000Z']</t>
         </is>
       </c>
       <c r="M186" t="inlineStr">
@@ -14690,7 +14690,7 @@
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>['2023-11-01T00:00:00.000Z', '2026-09-11T13:30:00.000Z']</t>
+          <t>['2023-11-01T00:00:00.000Z', '2026-09-18T19:10:00.000Z']</t>
         </is>
       </c>
       <c r="M187" t="inlineStr">
@@ -14766,7 +14766,7 @@
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-09-06T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-09-13T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M188" t="inlineStr">
@@ -14844,7 +14844,7 @@
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>['1993-01-06T00:00:00.000Z', '2026-09-02T00:00:00.000Z']</t>
+          <t>['1993-01-06T00:00:00.000Z', '2026-09-09T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M189" t="inlineStr">
@@ -14994,7 +14994,7 @@
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-09-11T23:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-09-18T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M191" t="inlineStr">
@@ -15148,7 +15148,7 @@
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>['2010-01-12T00:00:00.000Z', '2026-09-11T00:00:00.000Z']</t>
+          <t>['2010-01-12T00:00:00.000Z', '2026-09-18T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M193" t="inlineStr">
@@ -15300,7 +15300,7 @@
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-09-06T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-09-13T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M195" t="inlineStr">
@@ -15426,7 +15426,7 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>['Global Ocean']</t>
+          <t>['Global Ocean', 'Atlantic: NW', 'Atlantic: North']</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
@@ -15454,7 +15454,7 @@
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>['2025-05-21T00:00:00.000Z', '2026-09-14T18:00:00.000Z']</t>
+          <t>['2025-05-21T00:00:00.000Z', '2026-09-21T18:00:00.000Z']</t>
         </is>
       </c>
       <c r="M197" t="inlineStr">

--- a/outputs/excel/copernicus_marine.xlsx
+++ b/outputs/excel/copernicus_marine.xlsx
@@ -564,7 +564,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>['2020-11-01T00:00:00.000Z', '2026-09-29T00:00:00.000Z']</t>
+          <t>['2020-11-01T00:00:00.000Z', '2026-10-06T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -640,7 +640,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>['2022-11-01T03:00:00.000Z', '2026-09-29T00:00:00.000Z']</t>
+          <t>['2022-11-01T03:00:00.000Z', '2026-10-06T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>['2021-10-01T00:00:00.000Z', '2026-09-28T00:00:00.000Z']</t>
+          <t>['2021-10-01T00:00:00.000Z', '2026-10-05T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>['2021-07-05T00:00:00.000Z', '2026-09-28T23:00:00.000Z']</t>
+          <t>['2021-07-05T00:00:00.000Z', '2026-10-05T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>['2022-08-01T00:00:00.000Z', '2026-09-20T23:00:00.000Z']</t>
+          <t>['2022-08-01T00:00:00.000Z', '2026-10-01T12:00:00.000Z']</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1346,7 +1346,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>['2019-01-01T00:00:00.000Z', '2026-09-28T00:00:00.000Z']</t>
+          <t>['2019-01-01T00:00:00.000Z', '2026-10-05T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>['2019-08-01T00:00:00.000Z', '2026-09-26T23:00:00.000Z']</t>
+          <t>['2019-08-01T00:00:00.000Z', '2026-10-03T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-09-28T23:45:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-10-05T23:45:00.000Z']</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1664,7 +1664,7 @@
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2025-12-31T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-05-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>['2021-11-01T00:00:00.000Z', '2026-09-28T12:00:00.000Z']</t>
+          <t>['2021-11-01T00:00:00.000Z', '2026-10-05T12:00:00.000Z']</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>['2021-10-01T01:00:00.000Z', '2026-09-28T12:00:00.000Z']</t>
+          <t>['2021-10-01T01:00:00.000Z', '2026-10-05T12:00:00.000Z']</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2050,7 +2050,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>['2022-11-01T00:00:00.000Z', '2026-09-27T00:00:00.000Z']</t>
+          <t>['2022-11-01T00:00:00.000Z', '2026-10-04T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2128,7 +2128,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-05-31T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-07-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-05-31T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-07-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>['2021-11-01T00:00:00.000Z', '2026-09-28T00:00:00.000Z']</t>
+          <t>['2021-11-01T00:00:00.000Z', '2026-10-05T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2436,7 +2436,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>['2022-12-18T00:00:00.000Z', '2026-09-29T11:00:00.000Z']</t>
+          <t>['2022-12-18T00:00:00.000Z', '2026-10-06T11:00:00.000Z']</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>['2023-10-01T00:00:00.000Z', '2026-09-28T23:00:00.000Z']</t>
+          <t>['2023-10-01T00:00:00.000Z', '2026-10-05T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>['2022-11-22T00:00:00.000Z', '2026-09-29T00:00:00.000Z']</t>
+          <t>['2022-11-22T00:00:00.000Z', '2026-10-06T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2900,7 +2900,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>['2022-11-26T00:00:00.000Z', '2026-09-28T23:00:00.000Z']</t>
+          <t>['2022-11-26T00:00:00.000Z', '2026-10-05T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2978,7 +2978,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>['2022-11-23T00:00:00.000Z', '2026-09-26T00:00:00.000Z']</t>
+          <t>['2022-11-23T00:00:00.000Z', '2026-10-03T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3056,7 +3056,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-06-09T23:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-06-16T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -3210,7 +3210,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-06-09T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-06-16T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -3288,7 +3288,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>['2023-11-01T00:00:00.000Z', '2026-09-28T23:00:00.000Z']</t>
+          <t>['2023-11-01T00:00:00.000Z', '2026-10-05T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -3364,7 +3364,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>['2021-11-30T00:00:00.000Z', '2026-09-29T11:00:00.000Z']</t>
+          <t>['2021-11-30T00:00:00.000Z', '2026-10-06T11:00:00.000Z']</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -3442,7 +3442,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>['2023-10-01T00:00:00.000Z', '2026-09-28T00:00:00.000Z']</t>
+          <t>['2023-10-01T00:00:00.000Z', '2026-10-05T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>['1999-01-01T00:00:00.000Z', '2026-07-31T00:00:00.000Z']</t>
+          <t>['1999-01-01T00:00:00.000Z', '2026-08-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>['2024-08-02T00:00:00.000Z', '2026-09-26T00:00:00.000Z']</t>
+          <t>['2024-08-02T00:00:00.000Z', '2026-10-03T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3828,7 +3828,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>['2024-07-29T00:00:00.000Z', '2026-09-25T00:00:00.000Z']</t>
+          <t>['2024-07-29T00:00:00.000Z', '2026-10-02T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>['2024-08-06T00:00:00.000Z', '2026-09-25T23:00:00.000Z']</t>
+          <t>['2024-08-06T00:00:00.000Z', '2026-10-02T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3982,7 +3982,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>['2024-07-29T00:00:00.000Z', '2026-09-25T00:00:00.000Z']</t>
+          <t>['2024-07-29T00:00:00.000Z', '2026-10-02T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -4060,7 +4060,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-07-01T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-08-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>['1980-01-01T00:00:00.000Z', '2026-04-30T21:00:00.000Z']</t>
+          <t>['1980-01-01T00:00:00.000Z', '2026-05-31T21:00:00.000Z']</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-06-30T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-07-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -4290,7 +4290,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>['2022-05-03T00:00:00.000Z', '2026-09-19T16:03:06.770Z']</t>
+          <t>['2022-05-03T00:00:00.000Z', '2026-09-26T16:11:59.000Z']</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>['2022-10-04T00:00:00.000Z', '2026-09-20T00:00:00.000Z']</t>
+          <t>['2022-10-04T00:00:00.000Z', '2026-09-27T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -4662,7 +4662,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>['2022-03-14T01:03:00.000Z', '2026-09-19T12:55:22.151Z']</t>
+          <t>['2022-03-14T01:03:00.000Z', '2026-09-26T13:11:58.314Z']</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -4738,7 +4738,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>['2022-10-04T00:00:00.000Z', '2026-09-20T00:00:00.000Z']</t>
+          <t>['2022-10-04T00:00:00.000Z', '2026-09-27T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -5338,7 +5338,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>['2026-08-26T00:00:00.000Z', '2026-09-18T00:00:00.000Z']</t>
+          <t>['2026-09-07T00:00:00.000Z', '2026-09-25T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -5414,7 +5414,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>['2023-04-01T00:00:00.000Z', '2026-09-18T00:00:00.000Z']</t>
+          <t>['2023-04-01T00:00:00.000Z', '2026-09-25T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -5794,7 +5794,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>['2026-08-31T00:00:00.000Z', '2026-09-18T00:00:00.000Z']</t>
+          <t>['2026-09-08T00:00:00.000Z', '2026-09-25T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -5870,7 +5870,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>['2026-06-01T00:00:00.000Z', '2026-09-18T00:00:00.000Z']</t>
+          <t>['2026-06-01T00:00:00.000Z', '2026-09-25T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -5946,7 +5946,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-09-18T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-09-25T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -6022,7 +6022,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>['2020-01-08T00:00:00.000Z', '2026-08-01T00:00:00.000Z']</t>
+          <t>['2020-01-08T00:00:00.000Z', '2026-08-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -6098,7 +6098,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>['2026-09-04T00:00:00.000Z', '2026-09-18T00:00:00.000Z']</t>
+          <t>['2026-09-04T00:00:00.000Z', '2026-09-25T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-09-18T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-09-25T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -6326,7 +6326,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>['2020-01-02T00:00:00.000Z', '2026-08-01T00:00:00.000Z']</t>
+          <t>['2020-01-02T00:00:00.000Z', '2026-08-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -6402,7 +6402,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>['2026-09-04T00:00:00.000Z', '2026-09-18T00:00:00.000Z']</t>
+          <t>['2026-09-12T00:00:00.000Z', '2026-09-25T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -6478,7 +6478,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>['2025-12-01T00:00:00.000Z', '2026-09-18T00:00:00.000Z']</t>
+          <t>['2025-12-01T00:00:00.000Z', '2026-09-25T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -6554,7 +6554,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-09-18T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-09-25T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -6630,7 +6630,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-08-01T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-08-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
@@ -6706,7 +6706,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-09-18T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-09-25T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -6782,7 +6782,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-08-01T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-08-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
@@ -6858,7 +6858,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>['2026-09-04T00:00:00.000Z', '2026-09-18T00:00:00.000Z']</t>
+          <t>['2026-09-13T00:00:00.000Z', '2026-09-25T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -6934,7 +6934,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>['2022-01-01T00:00:00.000Z', '2026-09-18T00:00:00.000Z']</t>
+          <t>['2022-01-01T00:00:00.000Z', '2026-09-25T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -7010,7 +7010,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-09-18T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-09-25T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -7086,7 +7086,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>['2020-01-04T00:00:00.000Z', '2026-08-01T00:00:00.000Z']</t>
+          <t>['2020-01-04T00:00:00.000Z', '2026-08-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
@@ -7314,7 +7314,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-09-12T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-09-19T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -7390,7 +7390,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-09-11T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-09-18T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -7466,7 +7466,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-09-11T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-09-18T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -7618,7 +7618,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-09-11T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-09-19T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -7694,7 +7694,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-09-11T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-09-18T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -7770,7 +7770,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-09-11T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-09-18T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -7922,7 +7922,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>['1997-09-16T00:00:00.000Z', '2026-09-11T00:00:00.000Z']</t>
+          <t>['1997-09-16T00:00:00.000Z', '2026-09-18T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -7998,7 +7998,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-09-07T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-09-14T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
@@ -8074,7 +8074,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>['1997-09-16T00:00:00.000Z', '2026-09-11T00:00:00.000Z']</t>
+          <t>['1997-09-16T00:00:00.000Z', '2026-09-18T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
@@ -8150,7 +8150,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-09-07T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-09-14T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
@@ -8226,7 +8226,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>['2026-01-01T00:00:00.000Z', '2026-09-18T00:00:00.000Z']</t>
+          <t>['2026-01-01T00:00:00.000Z', '2026-09-25T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
@@ -8302,7 +8302,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>['2020-12-20T00:00:00.000Z', '2026-09-18T00:00:00.000Z']</t>
+          <t>['2020-12-20T00:00:00.000Z', '2026-09-25T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
@@ -8378,7 +8378,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>['2024-01-17T00:00:00.000Z', '2026-09-18T00:00:00.000Z']</t>
+          <t>['2024-01-17T00:00:00.000Z', '2026-09-25T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
@@ -8454,7 +8454,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>['2020-12-20T00:00:00.000Z', '2026-09-18T00:00:00.000Z']</t>
+          <t>['2020-12-20T00:00:00.000Z', '2026-09-25T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
@@ -8530,7 +8530,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-09-18T00:00:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-09-25T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
@@ -8606,7 +8606,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>['2019-03-11T00:00:00.000Z', '2026-09-19T00:00:00.000Z']</t>
+          <t>['2019-03-11T00:00:00.000Z', '2026-09-26T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
@@ -8682,7 +8682,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>['2024-06-19T00:00:00.000Z', '2026-09-19T00:00:00.000Z']</t>
+          <t>['2018-12-04T00:00:00.000Z', '2026-09-26T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
@@ -8758,7 +8758,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>['2022-05-01T00:00:00.000Z', '2026-09-18T23:00:00.000Z']</t>
+          <t>['2022-05-01T00:00:00.000Z', '2026-09-25T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-09-19T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-09-26T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
@@ -8910,7 +8910,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-09-19T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-09-26T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
@@ -8986,7 +8986,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-09-18T23:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-09-25T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
@@ -9062,7 +9062,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-09-19T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-09-26T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
@@ -9138,7 +9138,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-09-19T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-09-26T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
@@ -9214,7 +9214,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>['2019-01-01T00:00:00.000Z', '2026-09-18T23:00:00.000Z']</t>
+          <t>['2019-01-01T00:00:00.000Z', '2026-09-25T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
@@ -9830,7 +9830,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-08-20T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-08-27T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
@@ -9906,7 +9906,7 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-08-20T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-08-27T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
@@ -9982,7 +9982,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-08-20T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-08-27T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
@@ -10058,7 +10058,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-08-20T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-08-27T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
@@ -10134,7 +10134,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>['2022-01-01T00:00:00.000Z', '2026-09-18T00:00:00.000Z']</t>
+          <t>['2022-01-01T00:00:00.000Z', '2026-09-25T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
@@ -10210,7 +10210,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>['2023-10-18T00:00:00.000Z', '2026-09-14T00:00:00.000Z']</t>
+          <t>['2023-10-18T00:00:00.000Z', '2026-09-21T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
@@ -10286,7 +10286,7 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>['2022-01-02T00:00:00.000Z', '2026-09-19T12:00:00.000Z']</t>
+          <t>['2022-01-02T00:00:00.000Z', '2026-09-26T12:00:00.000Z']</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
@@ -10362,7 +10362,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>['2023-02-02T00:00:00.000Z', '2026-09-18T00:00:00.000Z']</t>
+          <t>['2023-02-02T00:00:00.000Z', '2026-09-25T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
@@ -10438,7 +10438,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>['2025-11-01T00:00:00.000Z', '2026-09-18T00:00:00.000Z']</t>
+          <t>['2025-11-01T00:00:00.000Z', '2026-09-25T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
@@ -10514,7 +10514,7 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-09-18T00:00:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-09-25T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
@@ -10590,7 +10590,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>['2020-09-01T12:10:00.000Z', '2026-09-18T21:10:00.000Z']</t>
+          <t>['2020-09-01T12:10:00.000Z', '2026-09-25T21:05:00.000Z']</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
@@ -10666,7 +10666,7 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>['2023-11-25T06:40:00.000Z', '2026-09-19T23:40:11.000Z']</t>
+          <t>['2023-11-25T06:40:00.000Z', '2026-09-27T01:07:49.000Z']</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
@@ -10742,7 +10742,7 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-09-19T00:00:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-09-26T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
@@ -10894,7 +10894,7 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>['1978-10-25T12:00:00.000Z', '2026-09-03T00:00:00.000Z']</t>
+          <t>['1978-10-25T12:00:00.000Z', '2026-09-10T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
@@ -11434,7 +11434,7 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>['2014-10-03T20:11:44.000Z', '2026-09-18T22:43:01.000Z']</t>
+          <t>['2014-10-03T20:11:44.000Z', '2026-09-25T19:13:27.000Z']</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
@@ -11510,7 +11510,7 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>['2014-10-03T00:00:00.000Z', '2026-09-18T00:00:00.000Z']</t>
+          <t>['2014-10-03T00:00:00.000Z', '2026-09-25T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
@@ -11742,7 +11742,7 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>['2016-01-01T00:00:00.000Z', '2026-09-18T00:00:00.000Z']</t>
+          <t>['2016-01-01T00:00:00.000Z', '2026-09-25T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
@@ -11814,7 +11814,7 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>['2024-06-13T04:00:00.000Z', '2026-09-18T23:00:00.000Z']</t>
+          <t>['2024-06-13T04:00:00.000Z', '2026-09-25T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
@@ -11890,7 +11890,7 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>['2024-04-01T00:00:00.000Z', '2026-09-19T00:00:00.000Z']</t>
+          <t>['2024-04-01T00:00:00.000Z', '2026-09-26T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
@@ -11966,7 +11966,7 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>['2024-06-27T00:00:00.000Z', '2026-09-19T00:00:00.000Z']</t>
+          <t>['2024-06-27T00:00:00.000Z', '2026-09-26T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
@@ -12042,7 +12042,7 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>['2024-06-27T00:00:00.000Z', '2026-09-19T00:00:00.000Z']</t>
+          <t>['2024-06-27T00:00:00.000Z', '2026-09-26T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
@@ -12118,7 +12118,7 @@
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>['2024-06-27T00:00:00.000Z', '2026-09-19T00:00:00.000Z']</t>
+          <t>['2024-06-27T00:00:00.000Z', '2026-09-26T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
@@ -12194,7 +12194,7 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>['2024-06-27T00:00:00.000Z', '2026-09-19T00:00:00.000Z']</t>
+          <t>['2024-06-27T00:00:00.000Z', '2026-09-26T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
@@ -12898,7 +12898,7 @@
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>['2023-11-21T00:00:00.000Z', '2026-09-19T23:01:15.000Z']</t>
+          <t>['2023-11-21T00:00:00.000Z', '2026-09-26T22:03:19.000Z']</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
@@ -12910,7 +12910,7 @@
         <v>0</v>
       </c>
       <c r="O163" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="P163" t="inlineStr">
         <is>
@@ -12974,7 +12974,7 @@
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>['2021-01-01T00:00:00.000Z', '2026-09-18T18:00:00.000Z']</t>
+          <t>['2021-01-01T00:00:00.000Z', '2026-09-25T18:00:00.000Z']</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
@@ -13580,7 +13580,7 @@
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>['1986-06-02T09:00:00.000Z', '2026-09-19T07:13:07.000Z']</t>
+          <t>['1986-06-02T09:00:00.000Z', '2026-09-26T07:07:30.000Z']</t>
         </is>
       </c>
       <c r="M172" t="inlineStr">
@@ -13652,7 +13652,7 @@
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-09-19T23:30:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-09-26T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M173" t="inlineStr">
@@ -14254,7 +14254,7 @@
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>['1841-03-21T00:00:00.000Z', '2026-09-19T23:20:00.000Z']</t>
+          <t>['1841-03-21T00:00:00.000Z', '2026-09-26T23:20:00.000Z']</t>
         </is>
       </c>
       <c r="M181" t="inlineStr">
@@ -14326,7 +14326,7 @@
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>['1860-05-24T07:00:00.000Z', '2026-09-19T22:19:00.000Z']</t>
+          <t>['1860-05-24T07:00:00.000Z', '2026-09-26T22:26:00.000Z']</t>
         </is>
       </c>
       <c r="M182" t="inlineStr">
@@ -14398,7 +14398,7 @@
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>['1841-03-21T00:00:00.000Z', '2026-09-19T18:44:00.000Z']</t>
+          <t>['1841-03-21T00:00:00.000Z', '2026-09-26T18:44:00.000Z']</t>
         </is>
       </c>
       <c r="M183" t="inlineStr">
@@ -14470,7 +14470,7 @@
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-09-20T00:13:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-09-26T23:20:00.000Z']</t>
         </is>
       </c>
       <c r="M184" t="inlineStr">
@@ -14542,7 +14542,7 @@
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-09-19T21:13:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-09-26T21:19:00.000Z']</t>
         </is>
       </c>
       <c r="M185" t="inlineStr">
@@ -14614,7 +14614,7 @@
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-09-19T23:20:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-09-26T23:20:00.000Z']</t>
         </is>
       </c>
       <c r="M186" t="inlineStr">
@@ -14690,7 +14690,7 @@
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>['2023-11-01T00:00:00.000Z', '2026-09-18T19:10:00.000Z']</t>
+          <t>['2023-11-01T00:00:00.000Z', '2026-09-25T19:50:00.000Z']</t>
         </is>
       </c>
       <c r="M187" t="inlineStr">
@@ -14766,7 +14766,7 @@
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-09-13T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-09-20T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M188" t="inlineStr">
@@ -14844,7 +14844,7 @@
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>['1993-01-06T00:00:00.000Z', '2026-09-09T00:00:00.000Z']</t>
+          <t>['1993-01-06T00:00:00.000Z', '2026-09-16T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M189" t="inlineStr">
@@ -14994,7 +14994,7 @@
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-09-18T23:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-09-25T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M191" t="inlineStr">
@@ -15148,7 +15148,7 @@
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>['2010-01-12T00:00:00.000Z', '2026-09-18T00:00:00.000Z']</t>
+          <t>['2010-01-12T00:00:00.000Z', '2026-09-25T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M193" t="inlineStr">
@@ -15300,7 +15300,7 @@
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-09-13T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-09-20T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M195" t="inlineStr">
@@ -15454,7 +15454,7 @@
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>['2025-05-21T00:00:00.000Z', '2026-09-21T18:00:00.000Z']</t>
+          <t>['2025-05-21T00:00:00.000Z', '2026-09-28T18:00:00.000Z']</t>
         </is>
       </c>
       <c r="M197" t="inlineStr">

--- a/outputs/excel/copernicus_marine.xlsx
+++ b/outputs/excel/copernicus_marine.xlsx
@@ -564,7 +564,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>['2020-11-01T00:00:00.000Z', '2026-10-06T00:00:00.000Z']</t>
+          <t>['2020-11-01T00:00:00.000Z', '2026-10-13T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -640,7 +640,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>['2022-11-01T03:00:00.000Z', '2026-10-06T00:00:00.000Z']</t>
+          <t>['2022-11-01T03:00:00.000Z', '2026-10-13T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>['2021-10-01T00:00:00.000Z', '2026-10-05T00:00:00.000Z']</t>
+          <t>['2021-10-01T00:00:00.000Z', '2026-10-13T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>['1998-01-01T00:00:00.000Z', '2025-06-30T00:00:00.000Z']</t>
+          <t>['1998-01-01T00:00:00.000Z', '2025-12-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>['2021-07-05T00:00:00.000Z', '2026-10-05T23:00:00.000Z']</t>
+          <t>['2021-07-05T00:00:00.000Z', '2026-10-12T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>['2022-08-01T00:00:00.000Z', '2026-10-01T12:00:00.000Z']</t>
+          <t>['2022-08-01T00:00:00.000Z', '2026-10-09T12:00:00.000Z']</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1346,7 +1346,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>['2019-01-01T00:00:00.000Z', '2026-10-05T00:00:00.000Z']</t>
+          <t>['2019-01-01T00:00:00.000Z', '2026-10-12T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>['2019-08-01T00:00:00.000Z', '2026-10-03T23:00:00.000Z']</t>
+          <t>['2019-08-01T00:00:00.000Z', '2026-10-09T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-10-05T23:45:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-10-12T23:45:00.000Z']</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>['2021-11-01T00:00:00.000Z', '2026-10-05T12:00:00.000Z']</t>
+          <t>['2021-11-01T00:00:00.000Z', '2026-10-12T12:00:00.000Z']</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>['2021-10-01T01:00:00.000Z', '2026-10-05T12:00:00.000Z']</t>
+          <t>['2021-10-01T01:00:00.000Z', '2026-10-12T12:00:00.000Z']</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2050,7 +2050,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>['2022-11-01T00:00:00.000Z', '2026-10-04T00:00:00.000Z']</t>
+          <t>['2022-11-01T00:00:00.000Z', '2026-10-11T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>['2021-11-01T00:00:00.000Z', '2026-10-05T00:00:00.000Z']</t>
+          <t>['2021-11-01T00:00:00.000Z', '2026-10-12T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2436,7 +2436,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>['2022-12-18T00:00:00.000Z', '2026-10-06T11:00:00.000Z']</t>
+          <t>['2022-12-18T00:00:00.000Z', '2026-10-13T11:00:00.000Z']</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>['2023-10-01T00:00:00.000Z', '2026-10-05T23:00:00.000Z']</t>
+          <t>['2023-10-01T00:00:00.000Z', '2026-10-12T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>['2022-11-22T00:00:00.000Z', '2026-10-06T00:00:00.000Z']</t>
+          <t>['2022-11-22T00:00:00.000Z', '2026-10-13T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2900,7 +2900,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>['2022-11-26T00:00:00.000Z', '2026-10-05T23:00:00.000Z']</t>
+          <t>['2022-11-26T00:00:00.000Z', '2026-10-12T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2978,7 +2978,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>['2022-11-23T00:00:00.000Z', '2026-10-03T00:00:00.000Z']</t>
+          <t>['2022-11-23T00:00:00.000Z', '2026-10-10T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3288,7 +3288,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>['2023-11-01T00:00:00.000Z', '2026-10-05T23:00:00.000Z']</t>
+          <t>['2023-11-01T00:00:00.000Z', '2026-10-12T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -3364,7 +3364,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>['2021-11-30T00:00:00.000Z', '2026-10-06T11:00:00.000Z']</t>
+          <t>['2021-11-30T00:00:00.000Z', '2026-10-13T11:00:00.000Z']</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -3442,7 +3442,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>['2023-10-01T00:00:00.000Z', '2026-10-05T00:00:00.000Z']</t>
+          <t>['2023-10-01T00:00:00.000Z', '2026-10-12T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>['2024-08-02T00:00:00.000Z', '2026-10-03T00:00:00.000Z']</t>
+          <t>['2024-08-02T00:00:00.000Z', '2026-10-10T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3828,7 +3828,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>['2024-07-29T00:00:00.000Z', '2026-10-02T00:00:00.000Z']</t>
+          <t>['2024-07-29T00:00:00.000Z', '2026-10-09T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>['2024-08-06T00:00:00.000Z', '2026-10-02T23:00:00.000Z']</t>
+          <t>['2024-08-06T00:00:00.000Z', '2026-10-09T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3982,7 +3982,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>['2024-07-29T00:00:00.000Z', '2026-10-02T00:00:00.000Z']</t>
+          <t>['2024-07-29T00:00:00.000Z', '2026-10-09T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -4290,7 +4290,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>['2022-05-03T00:00:00.000Z', '2026-09-26T16:11:59.000Z']</t>
+          <t>['2022-05-03T00:00:00.000Z', '2026-10-03T15:56:08.556Z']</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>['2022-10-04T00:00:00.000Z', '2026-09-27T00:00:00.000Z']</t>
+          <t>['2022-10-04T00:00:00.000Z', '2026-10-04T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -4662,7 +4662,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>['2022-03-14T01:03:00.000Z', '2026-09-26T13:11:58.314Z']</t>
+          <t>['2022-03-14T01:03:00.000Z', '2026-10-03T14:35:44.535Z']</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -4738,7 +4738,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>['2022-10-04T00:00:00.000Z', '2026-09-27T00:00:00.000Z']</t>
+          <t>['2022-10-04T00:00:00.000Z', '2026-10-04T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -5038,7 +5038,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>['1992-10-13T00:32:22.000Z', '2026-01-16T23:51:46.000Z']</t>
+          <t>['1992-10-13T00:32:22.000Z', '2026-05-15T23:51:32.000Z']</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -5114,7 +5114,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-01-16T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-05-15T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -5190,7 +5190,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>['1992-10-13T05:51:26.000Z', '2026-01-16T23:01:27.000Z']</t>
+          <t>['1992-10-13T05:51:26.000Z', '2026-05-15T23:28:43.000Z']</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -5266,7 +5266,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-01-16T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-05-15T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -5338,7 +5338,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>['2026-09-07T00:00:00.000Z', '2026-09-25T00:00:00.000Z']</t>
+          <t>['2026-09-07T00:00:00.000Z', '2026-10-02T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -5414,7 +5414,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>['2023-04-01T00:00:00.000Z', '2026-09-25T00:00:00.000Z']</t>
+          <t>['2023-04-01T00:00:00.000Z', '2026-10-02T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -5794,7 +5794,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>['2026-09-08T00:00:00.000Z', '2026-09-25T00:00:00.000Z']</t>
+          <t>['2026-09-14T00:00:00.000Z', '2026-10-02T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -5870,7 +5870,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>['2026-06-01T00:00:00.000Z', '2026-09-25T00:00:00.000Z']</t>
+          <t>['2026-07-01T00:00:00.000Z', '2026-10-02T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -5946,7 +5946,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-09-25T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-10-02T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -6098,7 +6098,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>['2026-09-04T00:00:00.000Z', '2026-09-25T00:00:00.000Z']</t>
+          <t>['2026-09-23T00:00:00.000Z', '2026-10-02T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -6174,7 +6174,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>['2026-08-01T00:00:00.000Z', '2026-08-01T00:00:00.000Z']</t>
+          <t>['2026-09-01T00:00:00.000Z', '2026-09-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-09-25T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-10-02T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -6402,7 +6402,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>['2026-09-12T00:00:00.000Z', '2026-09-25T00:00:00.000Z']</t>
+          <t>['2026-09-20T00:00:00.000Z', '2026-10-02T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -6478,7 +6478,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>['2025-12-01T00:00:00.000Z', '2026-09-25T00:00:00.000Z']</t>
+          <t>['2025-12-01T00:00:00.000Z', '2026-10-02T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -6554,7 +6554,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-09-25T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-10-02T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -6706,7 +6706,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-09-25T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-10-02T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -6858,7 +6858,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>['2026-09-13T00:00:00.000Z', '2026-09-25T00:00:00.000Z']</t>
+          <t>['2026-09-22T00:00:00.000Z', '2026-10-02T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -6934,7 +6934,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>['2022-01-01T00:00:00.000Z', '2026-09-25T00:00:00.000Z']</t>
+          <t>['2022-01-01T00:00:00.000Z', '2026-10-02T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -7010,7 +7010,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-09-25T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-10-02T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -7314,7 +7314,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-09-19T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-09-26T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -7390,7 +7390,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-09-18T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-09-26T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -7466,7 +7466,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-09-18T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-09-25T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -7618,7 +7618,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-09-19T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-09-26T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -7694,7 +7694,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-09-18T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-09-25T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -7770,7 +7770,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-09-18T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-09-25T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -7922,7 +7922,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>['1997-09-16T00:00:00.000Z', '2026-09-18T00:00:00.000Z']</t>
+          <t>['1997-09-16T00:00:00.000Z', '2026-09-25T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -7998,7 +7998,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-09-14T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-09-21T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
@@ -8074,7 +8074,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>['1997-09-16T00:00:00.000Z', '2026-09-18T00:00:00.000Z']</t>
+          <t>['1997-09-16T00:00:00.000Z', '2026-09-25T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
@@ -8150,7 +8150,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-09-14T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-09-21T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
@@ -8226,7 +8226,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>['2026-01-01T00:00:00.000Z', '2026-09-25T00:00:00.000Z']</t>
+          <t>['2026-01-01T00:00:00.000Z', '2026-10-02T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
@@ -8302,7 +8302,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>['2020-12-20T00:00:00.000Z', '2026-09-25T00:00:00.000Z']</t>
+          <t>['2020-12-20T00:00:00.000Z', '2026-10-02T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
@@ -8378,7 +8378,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>['2024-01-17T00:00:00.000Z', '2026-09-25T00:00:00.000Z']</t>
+          <t>['2024-01-17T00:00:00.000Z', '2026-10-02T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
@@ -8454,7 +8454,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>['2020-12-20T00:00:00.000Z', '2026-09-25T00:00:00.000Z']</t>
+          <t>['2020-12-20T00:00:00.000Z', '2026-10-02T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
@@ -8530,7 +8530,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-09-25T00:00:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-10-02T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
@@ -8606,7 +8606,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>['2019-03-11T00:00:00.000Z', '2026-09-26T00:00:00.000Z']</t>
+          <t>['2019-03-11T00:00:00.000Z', '2026-10-03T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
@@ -8682,7 +8682,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>['2018-12-04T00:00:00.000Z', '2026-09-26T00:00:00.000Z']</t>
+          <t>['2018-12-04T00:00:00.000Z', '2026-10-03T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
@@ -8758,7 +8758,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>['2022-05-01T00:00:00.000Z', '2026-09-25T23:00:00.000Z']</t>
+          <t>['2022-05-01T00:00:00.000Z', '2026-10-02T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-09-26T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-10-03T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
@@ -8910,7 +8910,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-09-26T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-10-03T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
@@ -8986,7 +8986,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-09-25T23:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-10-02T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
@@ -9062,7 +9062,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-09-26T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-10-03T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
@@ -9138,7 +9138,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-09-26T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-10-03T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
@@ -9214,7 +9214,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>['2019-01-01T00:00:00.000Z', '2026-09-25T23:00:00.000Z']</t>
+          <t>['2019-01-01T00:00:00.000Z', '2026-10-02T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
@@ -9678,7 +9678,7 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2024-12-31T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2025-12-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
@@ -9830,7 +9830,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-08-27T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-09-03T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
@@ -9906,7 +9906,7 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-08-27T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-09-03T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
@@ -9982,7 +9982,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-08-27T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-09-03T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
@@ -10058,7 +10058,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-08-27T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-09-03T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
@@ -10134,7 +10134,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>['2022-01-01T00:00:00.000Z', '2026-09-25T00:00:00.000Z']</t>
+          <t>['2022-01-01T00:00:00.000Z', '2026-10-03T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
@@ -10210,7 +10210,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>['2023-10-18T00:00:00.000Z', '2026-09-21T00:00:00.000Z']</t>
+          <t>['2023-10-18T00:00:00.000Z', '2026-09-28T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
@@ -10286,7 +10286,7 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>['2022-01-02T00:00:00.000Z', '2026-09-26T12:00:00.000Z']</t>
+          <t>['2022-01-02T00:00:00.000Z', '2026-10-03T12:00:00.000Z']</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
@@ -10362,7 +10362,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>['2023-02-02T00:00:00.000Z', '2026-09-25T00:00:00.000Z']</t>
+          <t>['2023-02-02T00:00:00.000Z', '2026-10-02T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
@@ -10438,7 +10438,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>['2025-11-01T00:00:00.000Z', '2026-09-25T00:00:00.000Z']</t>
+          <t>['2025-11-01T00:00:00.000Z', '2026-10-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
@@ -10514,7 +10514,7 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-09-25T00:00:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-10-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
@@ -10590,7 +10590,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>['2020-09-01T12:10:00.000Z', '2026-09-25T21:05:00.000Z']</t>
+          <t>['2020-09-01T12:10:00.000Z', '2026-10-02T22:10:00.000Z']</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
@@ -10666,7 +10666,7 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>['2023-11-25T06:40:00.000Z', '2026-09-27T01:07:49.000Z']</t>
+          <t>['2023-11-25T06:40:00.000Z', '2026-10-04T00:27:58.000Z']</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
@@ -10742,7 +10742,7 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-09-26T00:00:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-10-03T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
@@ -10894,7 +10894,7 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>['1978-10-25T12:00:00.000Z', '2026-09-10T00:00:00.000Z']</t>
+          <t>['1978-10-25T12:00:00.000Z', '2026-09-17T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
@@ -11434,7 +11434,7 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>['2014-10-03T20:11:44.000Z', '2026-09-25T19:13:27.000Z']</t>
+          <t>['2014-10-03T20:11:44.000Z', '2026-10-02T23:48:08.000Z']</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
@@ -11510,7 +11510,7 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>['2014-10-03T00:00:00.000Z', '2026-09-25T00:00:00.000Z']</t>
+          <t>['2014-10-03T00:00:00.000Z', '2026-10-02T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
@@ -11742,7 +11742,7 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>['2016-01-01T00:00:00.000Z', '2026-09-25T00:00:00.000Z']</t>
+          <t>['2016-01-01T00:00:00.000Z', '2026-10-02T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
@@ -11814,7 +11814,7 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>['2024-06-13T04:00:00.000Z', '2026-09-25T23:00:00.000Z']</t>
+          <t>['2024-06-13T04:00:00.000Z', '2026-10-02T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
@@ -11890,7 +11890,7 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>['2024-04-01T00:00:00.000Z', '2026-09-26T00:00:00.000Z']</t>
+          <t>['2024-04-01T00:00:00.000Z', '2026-10-03T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
@@ -11966,7 +11966,7 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>['2024-06-27T00:00:00.000Z', '2026-09-26T00:00:00.000Z']</t>
+          <t>['2024-06-27T00:00:00.000Z', '2026-10-03T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
@@ -12042,7 +12042,7 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>['2024-06-27T00:00:00.000Z', '2026-09-26T00:00:00.000Z']</t>
+          <t>['2024-06-27T00:00:00.000Z', '2026-10-03T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
@@ -12118,7 +12118,7 @@
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>['2024-06-27T00:00:00.000Z', '2026-09-26T00:00:00.000Z']</t>
+          <t>['2024-06-27T00:00:00.000Z', '2026-10-03T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
@@ -12194,7 +12194,7 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>['2024-06-27T00:00:00.000Z', '2026-09-26T00:00:00.000Z']</t>
+          <t>['2024-06-27T00:00:00.000Z', '2026-10-03T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
@@ -12898,7 +12898,7 @@
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>['2023-11-21T00:00:00.000Z', '2026-09-26T22:03:19.000Z']</t>
+          <t>['2023-11-21T00:00:00.000Z', '2026-10-03T22:30:08.000Z']</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
@@ -12974,7 +12974,7 @@
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>['2021-01-01T00:00:00.000Z', '2026-09-25T18:00:00.000Z']</t>
+          <t>['2021-01-01T00:00:00.000Z', '2026-10-02T18:00:00.000Z']</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
@@ -13122,7 +13122,7 @@
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>['2021-11-01T00:00:00.000Z', '2026-09-30T21:00:00.000Z']</t>
+          <t>['2021-11-01T00:00:00.000Z', '2026-10-14T21:00:00.000Z']</t>
         </is>
       </c>
       <c r="M166" t="inlineStr">
@@ -13580,7 +13580,7 @@
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>['1986-06-02T09:00:00.000Z', '2026-09-26T07:07:30.000Z']</t>
+          <t>['1986-06-02T09:00:00.000Z', '2026-10-03T07:18:45.000Z']</t>
         </is>
       </c>
       <c r="M172" t="inlineStr">
@@ -13652,7 +13652,7 @@
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-09-26T23:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-10-03T23:59:00.000Z']</t>
         </is>
       </c>
       <c r="M173" t="inlineStr">
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="O173" t="n">
-        <v>839</v>
+        <v>854</v>
       </c>
       <c r="P173" t="inlineStr">
         <is>
@@ -14254,7 +14254,7 @@
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>['1841-03-21T00:00:00.000Z', '2026-09-26T23:20:00.000Z']</t>
+          <t>['1841-03-21T00:00:00.000Z', '2026-10-03T23:20:00.000Z']</t>
         </is>
       </c>
       <c r="M181" t="inlineStr">
@@ -14326,7 +14326,7 @@
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>['1860-05-24T07:00:00.000Z', '2026-09-26T22:26:00.000Z']</t>
+          <t>['1860-05-24T07:00:00.000Z', '2026-10-03T22:16:00.000Z']</t>
         </is>
       </c>
       <c r="M182" t="inlineStr">
@@ -14398,7 +14398,7 @@
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>['1841-03-21T00:00:00.000Z', '2026-09-26T18:44:00.000Z']</t>
+          <t>['1841-03-21T00:00:00.000Z', '2026-10-03T18:44:00.000Z']</t>
         </is>
       </c>
       <c r="M183" t="inlineStr">
@@ -14470,7 +14470,7 @@
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-09-26T23:20:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-10-03T23:20:00.000Z']</t>
         </is>
       </c>
       <c r="M184" t="inlineStr">
@@ -14542,7 +14542,7 @@
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-09-26T21:19:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-10-03T21:14:00.000Z']</t>
         </is>
       </c>
       <c r="M185" t="inlineStr">
@@ -14614,7 +14614,7 @@
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-09-26T23:20:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-10-04T01:10:00.000Z']</t>
         </is>
       </c>
       <c r="M186" t="inlineStr">
@@ -14690,7 +14690,7 @@
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>['2023-11-01T00:00:00.000Z', '2026-09-25T19:50:00.000Z']</t>
+          <t>['2023-11-01T00:00:00.000Z', '2026-10-02T19:50:00.000Z']</t>
         </is>
       </c>
       <c r="M187" t="inlineStr">
@@ -14766,7 +14766,7 @@
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-09-20T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-09-27T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M188" t="inlineStr">
@@ -14844,7 +14844,7 @@
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>['1993-01-06T00:00:00.000Z', '2026-09-16T00:00:00.000Z']</t>
+          <t>['1993-01-06T00:00:00.000Z', '2026-09-23T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M189" t="inlineStr">
@@ -14994,7 +14994,7 @@
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-09-25T23:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-10-02T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M191" t="inlineStr">
@@ -15148,7 +15148,7 @@
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>['2010-01-12T00:00:00.000Z', '2026-09-25T00:00:00.000Z']</t>
+          <t>['2010-01-12T00:00:00.000Z', '2026-10-02T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M193" t="inlineStr">
@@ -15300,7 +15300,7 @@
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-09-20T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-09-27T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M195" t="inlineStr">
@@ -15454,7 +15454,7 @@
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>['2025-05-21T00:00:00.000Z', '2026-09-28T18:00:00.000Z']</t>
+          <t>['2025-05-21T00:00:00.000Z', '2026-10-05T18:00:00.000Z']</t>
         </is>
       </c>
       <c r="M197" t="inlineStr">

--- a/outputs/excel/copernicus_marine.xlsx
+++ b/outputs/excel/copernicus_marine.xlsx
@@ -564,7 +564,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>['2020-11-01T00:00:00.000Z', '2026-10-13T23:00:00.000Z']</t>
+          <t>['2020-11-01T00:00:00.000Z', '2026-10-20T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -640,7 +640,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>['2022-11-01T03:00:00.000Z', '2026-10-13T00:00:00.000Z']</t>
+          <t>['2022-11-01T03:00:00.000Z', '2026-10-20T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>['2021-10-01T00:00:00.000Z', '2026-10-13T00:00:00.000Z']</t>
+          <t>['2021-10-01T00:00:00.000Z', '2026-10-20T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-06-23T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-08-25T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2024-12-31T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2025-12-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>['1980-01-01T00:00:00.000Z', '2026-05-31T21:00:00.000Z']</t>
+          <t>['1980-01-01T00:00:00.000Z', '2026-07-31T21:00:00.000Z']</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-05-31T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-07-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>['2021-07-05T00:00:00.000Z', '2026-10-12T23:00:00.000Z']</t>
+          <t>['2021-07-05T00:00:00.000Z', '2026-10-19T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>['2022-08-01T00:00:00.000Z', '2026-10-09T12:00:00.000Z']</t>
+          <t>['2024-09-04T00:00:00.000Z', '2026-10-12T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1346,7 +1346,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>['2019-01-01T00:00:00.000Z', '2026-10-12T00:00:00.000Z']</t>
+          <t>['2019-01-01T00:00:00.000Z', '2026-10-19T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>['2019-08-01T00:00:00.000Z', '2026-10-09T23:00:00.000Z']</t>
+          <t>['2019-08-01T00:00:00.000Z', '2026-10-18T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-10-12T23:45:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-10-19T23:45:00.000Z']</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>['1964-01-01T00:00:00.000Z', '2025-07-31T23:00:00.000Z']</t>
+          <t>['1964-01-01T00:00:00.000Z', '2025-03-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1664,7 +1664,7 @@
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>['2021-11-01T00:00:00.000Z', '2026-10-12T12:00:00.000Z']</t>
+          <t>['2021-11-01T00:00:00.000Z', '2026-10-19T12:00:00.000Z']</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>['2021-10-01T01:00:00.000Z', '2026-10-12T12:00:00.000Z']</t>
+          <t>['2021-10-01T01:00:00.000Z', '2026-10-19T12:00:00.000Z']</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2050,7 +2050,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>['2022-11-01T00:00:00.000Z', '2026-10-11T00:00:00.000Z']</t>
+          <t>['2022-11-01T00:00:00.000Z', '2026-10-18T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>['2021-11-01T00:00:00.000Z', '2026-10-12T00:00:00.000Z']</t>
+          <t>['2021-11-01T00:00:00.000Z', '2026-10-19T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2436,7 +2436,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>['2022-12-18T00:00:00.000Z', '2026-10-13T11:00:00.000Z']</t>
+          <t>['2024-08-17T00:00:00.000Z', '2026-10-20T11:00:00.000Z']</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>['2023-10-01T00:00:00.000Z', '2026-10-12T23:00:00.000Z']</t>
+          <t>['2023-10-01T00:00:00.000Z', '2026-10-19T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2668,7 +2668,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>['1950-01-08T00:00:00.000Z', '2026-08-31T23:00:00.000Z']</t>
+          <t>['1950-01-08T00:00:00.000Z', '2026-09-30T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>['2022-11-22T00:00:00.000Z', '2026-10-13T00:00:00.000Z']</t>
+          <t>['2022-12-01T00:00:00.000Z', '2026-10-20T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2900,7 +2900,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>['2022-11-26T00:00:00.000Z', '2026-10-12T23:00:00.000Z']</t>
+          <t>['2022-11-26T00:00:00.000Z', '2026-10-19T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2978,7 +2978,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>['2022-11-23T00:00:00.000Z', '2026-10-10T00:00:00.000Z']</t>
+          <t>['2023-11-01T00:00:00.000Z', '2026-10-17T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3132,7 +3132,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>['1980-01-01T00:00:00.000Z', '2026-05-30T23:00:00.000Z']</t>
+          <t>['1980-01-01T00:00:00.000Z', '2026-06-15T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -3288,7 +3288,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>['2023-11-01T00:00:00.000Z', '2026-10-12T23:00:00.000Z']</t>
+          <t>['2023-11-01T00:00:00.000Z', '2026-10-19T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -3364,7 +3364,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>['2021-11-30T00:00:00.000Z', '2026-10-13T11:00:00.000Z']</t>
+          <t>['2024-06-25T00:00:00.000Z', '2026-10-20T11:00:00.000Z']</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -3442,7 +3442,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>['2023-10-01T00:00:00.000Z', '2026-10-12T00:00:00.000Z']</t>
+          <t>['2023-10-01T00:00:00.000Z', '2026-10-19T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>['2024-08-02T00:00:00.000Z', '2026-10-10T00:00:00.000Z']</t>
+          <t>['2024-08-02T00:00:00.000Z', '2026-10-17T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3828,7 +3828,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>['2024-07-29T00:00:00.000Z', '2026-10-09T00:00:00.000Z']</t>
+          <t>['2024-07-29T00:00:00.000Z', '2026-10-16T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>['2024-08-06T00:00:00.000Z', '2026-10-09T23:00:00.000Z']</t>
+          <t>['2024-08-06T00:00:00.000Z', '2026-10-16T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3982,7 +3982,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>['2024-07-29T00:00:00.000Z', '2026-10-09T00:00:00.000Z']</t>
+          <t>['2024-07-29T00:00:00.000Z', '2026-10-16T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -4290,7 +4290,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>['2022-05-03T00:00:00.000Z', '2026-10-03T15:56:08.556Z']</t>
+          <t>['2022-05-03T00:00:00.000Z', '2026-10-10T15:56:59.768Z']</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>['2022-10-04T00:00:00.000Z', '2026-10-04T00:00:00.000Z']</t>
+          <t>['2022-10-04T00:00:00.000Z', '2026-10-11T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -4662,7 +4662,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>['2022-03-14T01:03:00.000Z', '2026-10-03T14:35:44.535Z']</t>
+          <t>['2022-03-14T01:03:00.000Z', '2026-10-10T14:00:05.974Z']</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -4738,7 +4738,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>['2022-10-04T00:00:00.000Z', '2026-10-04T00:00:00.000Z']</t>
+          <t>['2022-10-04T00:00:00.000Z', '2026-10-11T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -5338,7 +5338,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>['2026-09-07T00:00:00.000Z', '2026-10-02T00:00:00.000Z']</t>
+          <t>['2026-09-19T00:00:00.000Z', '2026-10-09T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -5414,7 +5414,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>['2023-04-01T00:00:00.000Z', '2026-10-02T00:00:00.000Z']</t>
+          <t>['2023-04-01T00:00:00.000Z', '2026-10-09T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -5794,7 +5794,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>['2026-09-14T00:00:00.000Z', '2026-10-02T00:00:00.000Z']</t>
+          <t>['2026-09-24T00:00:00.000Z', '2026-10-09T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -5870,7 +5870,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>['2026-07-01T00:00:00.000Z', '2026-10-02T00:00:00.000Z']</t>
+          <t>['2026-09-01T00:00:00.000Z', '2026-10-09T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -5946,7 +5946,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-10-02T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-10-09T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -6022,7 +6022,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>['2020-01-08T00:00:00.000Z', '2026-08-31T00:00:00.000Z']</t>
+          <t>['2020-01-08T00:00:00.000Z', '2026-09-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -6098,7 +6098,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>['2026-09-23T00:00:00.000Z', '2026-10-02T00:00:00.000Z']</t>
+          <t>['2026-09-23T00:00:00.000Z', '2026-10-09T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-10-02T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-10-09T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -6326,7 +6326,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>['2020-01-02T00:00:00.000Z', '2026-08-31T00:00:00.000Z']</t>
+          <t>['2020-01-02T00:00:00.000Z', '2026-09-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -6402,7 +6402,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>['2026-09-20T00:00:00.000Z', '2026-10-02T00:00:00.000Z']</t>
+          <t>['2026-09-25T00:00:00.000Z', '2026-10-09T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -6478,7 +6478,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>['2025-12-01T00:00:00.000Z', '2026-10-02T00:00:00.000Z']</t>
+          <t>['2025-12-01T00:00:00.000Z', '2026-10-09T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -6554,7 +6554,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-10-02T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-10-09T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -6630,7 +6630,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-08-31T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-09-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
@@ -6706,7 +6706,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-10-02T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-10-09T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -6782,7 +6782,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-08-31T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-09-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
@@ -6858,7 +6858,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>['2026-09-22T00:00:00.000Z', '2026-10-02T00:00:00.000Z']</t>
+          <t>['2026-10-01T00:00:00.000Z', '2026-10-09T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -6934,7 +6934,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>['2022-01-01T00:00:00.000Z', '2026-10-02T00:00:00.000Z']</t>
+          <t>['2022-01-01T00:00:00.000Z', '2026-10-09T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -7010,7 +7010,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-10-02T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-10-09T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -7086,7 +7086,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>['2020-01-04T00:00:00.000Z', '2026-08-31T00:00:00.000Z']</t>
+          <t>['2020-01-04T00:00:00.000Z', '2026-09-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
@@ -7314,7 +7314,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-09-26T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-10-03T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -7390,7 +7390,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-09-26T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-10-02T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -7466,7 +7466,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-09-25T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-10-02T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -7618,7 +7618,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-09-26T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-10-02T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -7694,7 +7694,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-09-25T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-10-02T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -7770,7 +7770,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-09-25T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-10-02T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-08-01T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-09-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
@@ -7922,7 +7922,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>['1997-09-16T00:00:00.000Z', '2026-09-25T00:00:00.000Z']</t>
+          <t>['1997-09-16T00:00:00.000Z', '2026-10-02T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -7998,7 +7998,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-09-21T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-09-30T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
@@ -8074,7 +8074,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>['1997-09-16T00:00:00.000Z', '2026-09-25T00:00:00.000Z']</t>
+          <t>['1997-09-16T00:00:00.000Z', '2026-10-02T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
@@ -8150,7 +8150,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-09-21T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-09-30T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
@@ -8226,7 +8226,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>['2026-01-01T00:00:00.000Z', '2026-10-02T00:00:00.000Z']</t>
+          <t>['2026-01-01T00:00:00.000Z', '2026-10-09T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
@@ -8302,7 +8302,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>['2020-12-20T00:00:00.000Z', '2026-10-02T00:00:00.000Z']</t>
+          <t>['2020-12-20T00:00:00.000Z', '2026-10-09T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
@@ -8378,7 +8378,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>['2024-01-17T00:00:00.000Z', '2026-10-02T00:00:00.000Z']</t>
+          <t>['2024-01-17T00:00:00.000Z', '2026-10-09T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
@@ -8454,7 +8454,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>['2020-12-20T00:00:00.000Z', '2026-10-02T00:00:00.000Z']</t>
+          <t>['2020-12-20T00:00:00.000Z', '2026-10-09T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
@@ -8530,7 +8530,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-10-02T00:00:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-10-09T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
@@ -8606,7 +8606,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>['2019-03-11T00:00:00.000Z', '2026-10-03T00:00:00.000Z']</t>
+          <t>['2019-03-11T00:00:00.000Z', '2026-10-10T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
@@ -8682,7 +8682,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>['2018-12-04T00:00:00.000Z', '2026-10-03T00:00:00.000Z']</t>
+          <t>['2018-12-04T00:00:00.000Z', '2026-10-10T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
@@ -8758,7 +8758,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>['2022-05-01T00:00:00.000Z', '2026-10-02T23:00:00.000Z']</t>
+          <t>['2022-05-01T00:00:00.000Z', '2026-10-09T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-10-03T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-10-10T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
@@ -8910,7 +8910,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-10-03T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-10-10T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
@@ -8986,7 +8986,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-10-02T23:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-10-09T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
@@ -9062,7 +9062,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-10-03T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-10-10T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
@@ -9138,7 +9138,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-10-03T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-10-10T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
@@ -9214,7 +9214,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>['2019-01-01T00:00:00.000Z', '2026-10-02T23:00:00.000Z']</t>
+          <t>['2019-01-01T00:00:00.000Z', '2026-10-09T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
@@ -9370,7 +9370,7 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-05-13T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-09-19T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
@@ -9526,7 +9526,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-05-13T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-09-19T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
@@ -9678,7 +9678,7 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2025-12-31T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-06-30T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
@@ -9830,7 +9830,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-09-03T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-09-10T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
@@ -9906,7 +9906,7 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-09-03T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-09-10T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
@@ -9982,7 +9982,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-09-03T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-09-10T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
@@ -10058,7 +10058,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-09-03T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-09-10T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
@@ -10134,7 +10134,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>['2022-01-01T00:00:00.000Z', '2026-10-03T00:00:00.000Z']</t>
+          <t>['2024-05-20T00:00:00.000Z', '2026-10-10T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
@@ -10210,7 +10210,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>['2023-10-18T00:00:00.000Z', '2026-09-28T00:00:00.000Z']</t>
+          <t>['2023-10-18T00:00:00.000Z', '2026-10-05T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
@@ -10286,7 +10286,7 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>['2022-01-02T00:00:00.000Z', '2026-10-03T12:00:00.000Z']</t>
+          <t>['2024-06-02T00:00:00.000Z', '2026-10-10T12:00:00.000Z']</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
@@ -10362,7 +10362,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>['2023-02-02T00:00:00.000Z', '2026-10-02T00:00:00.000Z']</t>
+          <t>['2023-02-02T00:00:00.000Z', '2026-10-09T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
@@ -10438,7 +10438,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>['2025-11-01T00:00:00.000Z', '2026-10-01T00:00:00.000Z']</t>
+          <t>['2025-11-01T00:00:00.000Z', '2026-10-09T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
@@ -10514,7 +10514,7 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-10-01T00:00:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-10-09T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
@@ -10590,7 +10590,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>['2020-09-01T12:10:00.000Z', '2026-10-02T22:10:00.000Z']</t>
+          <t>['2020-09-01T12:10:00.000Z', '2026-10-10T08:25:00.000Z']</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
@@ -10666,7 +10666,7 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>['2023-11-25T06:40:00.000Z', '2026-10-04T00:27:58.000Z']</t>
+          <t>['2023-11-25T06:40:00.000Z', '2026-10-10T21:40:47.000Z']</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
@@ -10742,7 +10742,7 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-10-03T00:00:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-10-10T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
@@ -10894,7 +10894,7 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>['1978-10-25T12:00:00.000Z', '2026-09-17T00:00:00.000Z']</t>
+          <t>['1978-10-25T12:00:00.000Z', '2026-09-24T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
@@ -11050,7 +11050,7 @@
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>['2014-10-06T00:00:00.000Z', '2025-11-01T00:00:00.000Z']</t>
+          <t>['2014-10-06T00:00:00.000Z', '2026-10-05T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M139" t="inlineStr">
@@ -11202,7 +11202,7 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2024-12-31T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-06-30T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
@@ -11278,7 +11278,7 @@
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2024-12-31T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-06-30T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
@@ -11434,7 +11434,7 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>['2014-10-03T20:11:44.000Z', '2026-10-02T23:48:08.000Z']</t>
+          <t>['2014-10-03T20:11:44.000Z', '2026-10-09T23:24:57.000Z']</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
@@ -11510,7 +11510,7 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>['2014-10-03T00:00:00.000Z', '2026-10-02T00:00:00.000Z']</t>
+          <t>['2014-10-03T00:00:00.000Z', '2026-10-09T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
@@ -11742,7 +11742,7 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>['2016-01-01T00:00:00.000Z', '2026-10-02T00:00:00.000Z']</t>
+          <t>['2016-01-01T00:00:00.000Z', '2026-10-09T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
@@ -11814,7 +11814,7 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>['2024-06-13T04:00:00.000Z', '2026-10-02T23:00:00.000Z']</t>
+          <t>['2024-06-13T04:00:00.000Z', '2026-10-09T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
@@ -11890,7 +11890,7 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>['2024-04-01T00:00:00.000Z', '2026-10-03T00:00:00.000Z']</t>
+          <t>['2024-04-01T00:00:00.000Z', '2026-10-10T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
@@ -11966,7 +11966,7 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>['2024-06-27T00:00:00.000Z', '2026-10-03T00:00:00.000Z']</t>
+          <t>['2024-06-27T00:00:00.000Z', '2026-10-10T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
@@ -12042,7 +12042,7 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>['2024-06-27T00:00:00.000Z', '2026-10-03T00:00:00.000Z']</t>
+          <t>['2024-06-27T00:00:00.000Z', '2026-10-10T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
@@ -12118,7 +12118,7 @@
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>['2024-06-27T00:00:00.000Z', '2026-10-03T00:00:00.000Z']</t>
+          <t>['2024-06-27T00:00:00.000Z', '2026-10-10T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
@@ -12194,7 +12194,7 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>['2024-06-27T00:00:00.000Z', '2026-10-03T00:00:00.000Z']</t>
+          <t>['2024-06-27T00:00:00.000Z', '2026-10-10T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
@@ -12270,7 +12270,7 @@
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>['1991-08-01T00:00:00.000Z', '2026-05-31T00:00:00.000Z']</t>
+          <t>['1991-08-01T00:00:00.000Z', '2026-06-30T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M155" t="inlineStr">
@@ -12422,7 +12422,7 @@
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>['1994-07-01T00:00:00.000Z', '2026-05-01T00:00:00.000Z']</t>
+          <t>['1994-07-01T00:00:00.000Z', '2026-06-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M157" t="inlineStr">
@@ -12498,7 +12498,7 @@
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>['2018-03-13T00:00:00.000Z', '2025-07-26T00:00:00.000Z']</t>
+          <t>['2018-03-13T00:00:00.000Z', '2026-06-08T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M158" t="inlineStr">
@@ -12898,7 +12898,7 @@
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>['2023-11-21T00:00:00.000Z', '2026-10-03T22:30:08.000Z']</t>
+          <t>['2023-11-21T00:00:00.000Z', '2026-10-10T22:39:52.000Z']</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
@@ -12974,7 +12974,7 @@
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>['2021-01-01T00:00:00.000Z', '2026-10-02T18:00:00.000Z']</t>
+          <t>['2021-01-01T00:00:00.000Z', '2026-10-09T18:00:00.000Z']</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
@@ -13122,7 +13122,7 @@
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>['2021-11-01T00:00:00.000Z', '2026-10-14T21:00:00.000Z']</t>
+          <t>['2021-11-01T00:00:00.000Z', '2026-10-20T21:00:00.000Z']</t>
         </is>
       </c>
       <c r="M166" t="inlineStr">
@@ -13508,7 +13508,7 @@
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>['2024-06-01T00:00:00.000Z', '2026-08-01T00:00:00.000Z']</t>
+          <t>['2024-06-01T00:00:00.000Z', '2026-09-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M171" t="inlineStr">
@@ -13580,7 +13580,7 @@
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>['1986-06-02T09:00:00.000Z', '2026-10-03T07:18:45.000Z']</t>
+          <t>['1986-06-02T09:00:00.000Z', '2026-10-10T07:21:33.000Z']</t>
         </is>
       </c>
       <c r="M172" t="inlineStr">
@@ -13652,7 +13652,7 @@
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-10-03T23:59:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-10-10T23:40:00.000Z']</t>
         </is>
       </c>
       <c r="M173" t="inlineStr">
@@ -14097,12 +14097,12 @@
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>[-178.1602325439453, -66.66166687011719, 176.23199462890625, 78.92854309082031]</t>
+          <t>[-178.1602325439453, -77.8499984741211, 176.23199462890625, 78.92854309082031]</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>['1821-05-25T05:00:00.000Z', '2025-06-30T23:59:31.000Z']</t>
+          <t>['1821-05-25T05:00:00.000Z', '2025-12-31T23:59:55.000Z']</t>
         </is>
       </c>
       <c r="M179" t="inlineStr">
@@ -14254,7 +14254,7 @@
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>['1841-03-21T00:00:00.000Z', '2026-10-03T23:20:00.000Z']</t>
+          <t>['1841-03-21T00:00:00.000Z', '2026-10-10T23:20:00.000Z']</t>
         </is>
       </c>
       <c r="M181" t="inlineStr">
@@ -14326,7 +14326,7 @@
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>['1860-05-24T07:00:00.000Z', '2026-10-03T22:16:00.000Z']</t>
+          <t>['1860-05-24T07:00:00.000Z', '2026-10-10T22:27:00.000Z']</t>
         </is>
       </c>
       <c r="M182" t="inlineStr">
@@ -14398,7 +14398,7 @@
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>['1841-03-21T00:00:00.000Z', '2026-10-03T18:44:00.000Z']</t>
+          <t>['1841-03-21T00:00:00.000Z', '2026-10-10T18:38:00.000Z']</t>
         </is>
       </c>
       <c r="M183" t="inlineStr">
@@ -14470,7 +14470,7 @@
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-10-03T23:20:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-10-11T01:14:00.000Z']</t>
         </is>
       </c>
       <c r="M184" t="inlineStr">
@@ -14542,7 +14542,7 @@
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-10-03T21:14:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-10-09T03:04:00.000Z']</t>
         </is>
       </c>
       <c r="M185" t="inlineStr">
@@ -14614,7 +14614,7 @@
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-10-04T01:10:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-10-11T01:10:00.000Z']</t>
         </is>
       </c>
       <c r="M186" t="inlineStr">
@@ -14690,7 +14690,7 @@
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>['2023-11-01T00:00:00.000Z', '2026-10-02T19:50:00.000Z']</t>
+          <t>['2023-11-01T00:00:00.000Z', '2026-10-09T19:50:00.000Z']</t>
         </is>
       </c>
       <c r="M187" t="inlineStr">
@@ -14766,7 +14766,7 @@
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-09-27T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-10-04T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M188" t="inlineStr">
@@ -14994,7 +14994,7 @@
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-10-02T23:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-10-09T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M191" t="inlineStr">
@@ -15148,7 +15148,7 @@
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>['2010-01-12T00:00:00.000Z', '2026-10-02T00:00:00.000Z']</t>
+          <t>['2010-01-12T00:00:00.000Z', '2026-10-09T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M193" t="inlineStr">
@@ -15300,7 +15300,7 @@
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-09-27T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-10-04T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M195" t="inlineStr">
@@ -15376,7 +15376,7 @@
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>['1985-01-01T00:00:00.000Z', '2026-08-01T00:00:00.000Z']</t>
+          <t>['1985-01-01T00:00:00.000Z', '2026-09-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M196" t="inlineStr">
@@ -15454,7 +15454,7 @@
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>['2025-05-21T00:00:00.000Z', '2026-10-05T18:00:00.000Z']</t>
+          <t>['2025-05-21T00:00:00.000Z', '2026-10-12T18:00:00.000Z']</t>
         </is>
       </c>
       <c r="M197" t="inlineStr">
@@ -18526,7 +18526,7 @@
         <v>0</v>
       </c>
       <c r="O240" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P240" t="inlineStr"/>
       <c r="Q240" t="inlineStr">
@@ -18598,7 +18598,7 @@
         <v>0</v>
       </c>
       <c r="O241" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P241" t="inlineStr"/>
       <c r="Q241" t="inlineStr">
@@ -18670,7 +18670,7 @@
         <v>0</v>
       </c>
       <c r="O242" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P242" t="inlineStr"/>
       <c r="Q242" t="inlineStr">

--- a/outputs/excel/copernicus_marine.xlsx
+++ b/outputs/excel/copernicus_marine.xlsx
@@ -564,7 +564,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>['2020-11-01T00:00:00.000Z', '2026-10-20T23:00:00.000Z']</t>
+          <t>['2020-11-01T00:00:00.000Z', '2026-10-27T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -640,7 +640,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>['2022-11-01T03:00:00.000Z', '2026-10-20T00:00:00.000Z']</t>
+          <t>['2022-11-01T03:00:00.000Z', '2026-10-27T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>['2021-10-01T00:00:00.000Z', '2026-10-20T00:00:00.000Z']</t>
+          <t>['2021-10-01T00:00:00.000Z', '2026-10-26T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-07-31T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-08-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>['2021-07-05T00:00:00.000Z', '2026-10-19T23:00:00.000Z']</t>
+          <t>['2021-07-05T00:00:00.000Z', '2026-10-26T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>['2024-09-04T00:00:00.000Z', '2026-10-12T23:00:00.000Z']</t>
+          <t>['2024-09-04T00:00:00.000Z', '2026-10-22T11:00:00.000Z']</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1346,7 +1346,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>['2019-01-01T00:00:00.000Z', '2026-10-19T00:00:00.000Z']</t>
+          <t>['2019-01-01T00:00:00.000Z', '2026-10-26T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>['2019-08-01T00:00:00.000Z', '2026-10-18T23:00:00.000Z']</t>
+          <t>['2019-08-01T00:00:00.000Z', '2026-10-24T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-10-19T23:45:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-10-26T23:45:00.000Z']</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1664,7 +1664,7 @@
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>['2021-11-01T00:00:00.000Z', '2026-10-19T12:00:00.000Z']</t>
+          <t>['2021-11-01T00:00:00.000Z', '2026-10-26T12:00:00.000Z']</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>['2021-10-01T01:00:00.000Z', '2026-10-19T12:00:00.000Z']</t>
+          <t>['2021-10-01T01:00:00.000Z', '2026-10-26T12:00:00.000Z']</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2050,7 +2050,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>['2022-11-01T00:00:00.000Z', '2026-10-18T00:00:00.000Z']</t>
+          <t>['2022-11-01T00:00:00.000Z', '2026-10-25T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>['1980-01-01T01:00:00.000Z', '2026-07-01T00:00:00.000Z']</t>
+          <t>['1980-01-01T01:00:00.000Z', '2026-08-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>['2021-11-01T00:00:00.000Z', '2026-10-19T00:00:00.000Z']</t>
+          <t>['2021-11-01T00:00:00.000Z', '2026-10-26T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2436,7 +2436,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>['2024-08-17T00:00:00.000Z', '2026-10-20T11:00:00.000Z']</t>
+          <t>['2024-08-17T00:00:00.000Z', '2026-10-27T11:00:00.000Z']</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>['2023-10-01T00:00:00.000Z', '2026-10-19T23:00:00.000Z']</t>
+          <t>['2023-10-01T00:00:00.000Z', '2026-10-26T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-08-01T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-09-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>['1992-01-01T00:00:00.000Z', '2026-08-01T00:00:00.000Z']</t>
+          <t>['1992-01-01T00:00:00.000Z', '2026-09-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>['2022-12-01T00:00:00.000Z', '2026-10-20T00:00:00.000Z']</t>
+          <t>['2022-12-01T00:00:00.000Z', '2026-10-27T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2900,7 +2900,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>['2022-11-26T00:00:00.000Z', '2026-10-19T23:00:00.000Z']</t>
+          <t>['2022-11-26T00:00:00.000Z', '2026-10-26T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2978,7 +2978,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>['2023-11-01T00:00:00.000Z', '2026-10-17T00:00:00.000Z']</t>
+          <t>['2023-11-01T00:00:00.000Z', '2026-10-24T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3288,7 +3288,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>['2023-11-01T00:00:00.000Z', '2026-10-19T23:00:00.000Z']</t>
+          <t>['2023-11-01T00:00:00.000Z', '2026-10-26T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -3364,7 +3364,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>['2024-06-25T00:00:00.000Z', '2026-10-20T11:00:00.000Z']</t>
+          <t>['2024-06-25T00:00:00.000Z', '2026-10-27T11:00:00.000Z']</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -3442,7 +3442,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>['2023-10-01T00:00:00.000Z', '2026-10-19T00:00:00.000Z']</t>
+          <t>['2023-10-01T00:00:00.000Z', '2026-10-26T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -3520,7 +3520,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>['1987-01-01T00:00:00.000Z', '2026-08-31T23:00:00.000Z']</t>
+          <t>['1987-01-01T00:00:00.000Z', '2026-09-30T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>['2024-08-02T00:00:00.000Z', '2026-10-17T00:00:00.000Z']</t>
+          <t>['2024-08-02T00:00:00.000Z', '2026-10-24T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3828,7 +3828,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>['2024-07-29T00:00:00.000Z', '2026-10-16T00:00:00.000Z']</t>
+          <t>['2024-07-29T00:00:00.000Z', '2026-10-23T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>['2024-08-06T00:00:00.000Z', '2026-10-16T23:00:00.000Z']</t>
+          <t>['2024-08-06T00:00:00.000Z', '2026-10-23T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3982,7 +3982,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>['2024-07-29T00:00:00.000Z', '2026-10-16T00:00:00.000Z']</t>
+          <t>['2024-07-29T00:00:00.000Z', '2026-10-23T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -4290,7 +4290,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>['2022-05-03T00:00:00.000Z', '2026-10-10T15:56:59.768Z']</t>
+          <t>['2022-05-03T00:00:00.000Z', '2026-10-17T16:05:29.000Z']</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>['2022-10-04T00:00:00.000Z', '2026-10-11T00:00:00.000Z']</t>
+          <t>['2022-10-04T00:00:00.000Z', '2026-10-18T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -4662,7 +4662,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>['2022-03-14T01:03:00.000Z', '2026-10-10T14:00:05.974Z']</t>
+          <t>['2022-03-14T01:03:00.000Z', '2026-10-17T14:49:23.881Z']</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -4738,7 +4738,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>['2022-10-04T00:00:00.000Z', '2026-10-11T00:00:00.000Z']</t>
+          <t>['2022-10-04T00:00:00.000Z', '2026-10-18T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -5338,7 +5338,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>['2026-09-19T00:00:00.000Z', '2026-10-09T00:00:00.000Z']</t>
+          <t>['2026-09-30T00:00:00.000Z', '2026-10-16T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -5414,7 +5414,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>['2023-04-01T00:00:00.000Z', '2026-10-09T00:00:00.000Z']</t>
+          <t>['2023-04-01T00:00:00.000Z', '2026-10-16T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -5794,7 +5794,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>['2026-09-24T00:00:00.000Z', '2026-10-09T00:00:00.000Z']</t>
+          <t>['2026-09-29T00:00:00.000Z', '2026-10-16T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -5870,7 +5870,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>['2026-09-01T00:00:00.000Z', '2026-10-09T00:00:00.000Z']</t>
+          <t>['2026-09-01T00:00:00.000Z', '2026-10-16T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -5946,7 +5946,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-10-09T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-10-16T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -6098,7 +6098,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>['2026-09-23T00:00:00.000Z', '2026-10-09T00:00:00.000Z']</t>
+          <t>['2026-09-23T00:00:00.000Z', '2026-10-16T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-10-09T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-10-16T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -6402,7 +6402,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>['2026-09-25T00:00:00.000Z', '2026-10-09T00:00:00.000Z']</t>
+          <t>['2026-10-04T00:00:00.000Z', '2026-10-16T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -6478,7 +6478,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>['2025-12-01T00:00:00.000Z', '2026-10-09T00:00:00.000Z']</t>
+          <t>['2025-12-01T00:00:00.000Z', '2026-10-16T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -6554,7 +6554,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-10-09T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-10-16T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -6706,7 +6706,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-10-09T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-10-16T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -6858,7 +6858,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>['2026-10-01T00:00:00.000Z', '2026-10-09T00:00:00.000Z']</t>
+          <t>['2026-10-01T00:00:00.000Z', '2026-10-16T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -6934,7 +6934,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>['2022-01-01T00:00:00.000Z', '2026-10-09T00:00:00.000Z']</t>
+          <t>['2022-01-01T00:00:00.000Z', '2026-10-16T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -7010,7 +7010,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-10-09T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-10-16T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -7314,7 +7314,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-10-03T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-10-10T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -7390,7 +7390,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-10-02T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-10-09T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -7466,7 +7466,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-10-02T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-10-09T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -7618,7 +7618,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-10-02T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-10-09T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -7694,7 +7694,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-10-02T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-10-09T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -7770,7 +7770,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-10-02T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-10-09T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -7922,7 +7922,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>['1997-09-16T00:00:00.000Z', '2026-10-02T00:00:00.000Z']</t>
+          <t>['1997-09-16T00:00:00.000Z', '2026-10-09T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -7998,7 +7998,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-09-30T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-10-05T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
@@ -8074,7 +8074,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>['1997-09-16T00:00:00.000Z', '2026-10-02T00:00:00.000Z']</t>
+          <t>['1997-09-16T00:00:00.000Z', '2026-10-09T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
@@ -8150,7 +8150,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-09-30T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-10-05T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
@@ -8226,7 +8226,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>['2026-01-01T00:00:00.000Z', '2026-10-09T00:00:00.000Z']</t>
+          <t>['2026-01-01T00:00:00.000Z', '2026-10-16T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
@@ -8302,7 +8302,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>['2020-12-20T00:00:00.000Z', '2026-10-09T00:00:00.000Z']</t>
+          <t>['2020-12-20T00:00:00.000Z', '2026-10-16T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
@@ -8378,7 +8378,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>['2024-01-17T00:00:00.000Z', '2026-10-09T00:00:00.000Z']</t>
+          <t>['2024-01-17T00:00:00.000Z', '2026-10-16T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
@@ -8454,7 +8454,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>['2020-12-20T00:00:00.000Z', '2026-10-09T00:00:00.000Z']</t>
+          <t>['2020-12-20T00:00:00.000Z', '2026-10-16T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
@@ -8530,7 +8530,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-10-09T00:00:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-10-16T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
@@ -8606,7 +8606,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>['2019-03-11T00:00:00.000Z', '2026-10-10T00:00:00.000Z']</t>
+          <t>['2019-03-11T00:00:00.000Z', '2026-10-17T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
@@ -8682,7 +8682,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>['2018-12-04T00:00:00.000Z', '2026-10-10T00:00:00.000Z']</t>
+          <t>['2018-12-04T00:00:00.000Z', '2026-10-17T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
@@ -8758,7 +8758,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>['2022-05-01T00:00:00.000Z', '2026-10-09T23:00:00.000Z']</t>
+          <t>['2022-05-01T00:00:00.000Z', '2026-10-16T21:00:00.000Z']</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-10-10T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-10-17T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
@@ -8910,7 +8910,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-10-10T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-10-17T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
@@ -8986,7 +8986,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-10-09T23:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-10-16T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
@@ -9062,7 +9062,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-10-10T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-10-17T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
@@ -9138,7 +9138,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-10-10T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-10-17T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
@@ -9214,7 +9214,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>['2019-01-01T00:00:00.000Z', '2026-10-09T23:00:00.000Z']</t>
+          <t>['2019-01-01T00:00:00.000Z', '2026-10-16T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
@@ -9446,7 +9446,7 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>['1981-10-01T00:00:00.000Z', '2026-03-31T00:00:00.000Z']</t>
+          <t>['1981-10-01T00:00:00.000Z', '2026-06-30T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
@@ -9830,7 +9830,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-09-10T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-09-17T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
@@ -9906,7 +9906,7 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-09-10T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-09-17T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
@@ -9982,7 +9982,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-09-10T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-09-17T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
@@ -10058,7 +10058,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-09-10T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-09-17T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
@@ -10134,7 +10134,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>['2024-05-20T00:00:00.000Z', '2026-10-10T00:00:00.000Z']</t>
+          <t>['2024-05-20T00:00:00.000Z', '2026-10-16T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
@@ -10210,7 +10210,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>['2023-10-18T00:00:00.000Z', '2026-10-05T00:00:00.000Z']</t>
+          <t>['2023-10-18T00:00:00.000Z', '2026-10-12T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
@@ -10286,7 +10286,7 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>['2024-06-02T00:00:00.000Z', '2026-10-10T12:00:00.000Z']</t>
+          <t>['2024-06-02T00:00:00.000Z', '2026-10-17T12:00:00.000Z']</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
@@ -10362,7 +10362,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>['2023-02-02T00:00:00.000Z', '2026-10-09T00:00:00.000Z']</t>
+          <t>['2023-02-02T00:00:00.000Z', '2026-10-16T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
@@ -10438,7 +10438,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>['2025-11-01T00:00:00.000Z', '2026-10-09T00:00:00.000Z']</t>
+          <t>['2025-11-01T00:00:00.000Z', '2026-10-16T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
@@ -10514,7 +10514,7 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-10-09T00:00:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-10-16T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
@@ -10590,7 +10590,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>['2020-09-01T12:10:00.000Z', '2026-10-10T08:25:00.000Z']</t>
+          <t>['2020-09-01T12:10:00.000Z', '2026-10-16T21:30:00.000Z']</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
@@ -10666,7 +10666,7 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>['2023-11-25T06:40:00.000Z', '2026-10-10T21:40:47.000Z']</t>
+          <t>['2023-11-25T06:40:00.000Z', '2026-10-17T23:39:44.000Z']</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
@@ -10742,7 +10742,7 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-10-10T00:00:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-10-17T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
@@ -10894,7 +10894,7 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>['1978-10-25T12:00:00.000Z', '2026-09-24T00:00:00.000Z']</t>
+          <t>['1978-10-25T12:00:00.000Z', '2026-10-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
@@ -11126,7 +11126,7 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>['2003-04-01T00:00:00.000Z', '2026-06-30T00:00:00.000Z']</t>
+          <t>['2003-04-01T00:00:00.000Z', '2026-09-30T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
@@ -11358,7 +11358,7 @@
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>['1995-09-15T00:00:00.000Z', '2026-07-31T00:00:00.000Z']</t>
+          <t>['1995-09-15T00:00:00.000Z', '2026-09-30T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
@@ -11434,7 +11434,7 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>['2014-10-03T20:11:44.000Z', '2026-10-09T23:24:57.000Z']</t>
+          <t>['2014-10-03T20:11:44.000Z', '2026-10-16T22:57:46.000Z']</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
@@ -11510,7 +11510,7 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>['2014-10-03T00:00:00.000Z', '2026-10-09T00:00:00.000Z']</t>
+          <t>['2014-10-03T00:00:00.000Z', '2026-10-16T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
@@ -11742,7 +11742,7 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>['2016-01-01T00:00:00.000Z', '2026-10-09T00:00:00.000Z']</t>
+          <t>['2016-01-01T00:00:00.000Z', '2026-10-16T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
@@ -11814,7 +11814,7 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>['2024-06-13T04:00:00.000Z', '2026-10-09T23:00:00.000Z']</t>
+          <t>['2024-06-13T04:00:00.000Z', '2026-10-16T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
@@ -11890,7 +11890,7 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>['2024-04-01T00:00:00.000Z', '2026-10-10T00:00:00.000Z']</t>
+          <t>['2024-04-01T00:00:00.000Z', '2026-10-15T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
@@ -11966,7 +11966,7 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>['2024-06-27T00:00:00.000Z', '2026-10-10T00:00:00.000Z']</t>
+          <t>['2024-06-27T00:00:00.000Z', '2026-10-17T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
@@ -12042,7 +12042,7 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>['2024-06-27T00:00:00.000Z', '2026-10-10T00:00:00.000Z']</t>
+          <t>['2024-06-27T00:00:00.000Z', '2026-10-17T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
@@ -12118,7 +12118,7 @@
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>['2024-06-27T00:00:00.000Z', '2026-10-10T00:00:00.000Z']</t>
+          <t>['2024-06-27T00:00:00.000Z', '2026-10-17T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
@@ -12194,7 +12194,7 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>['2024-06-27T00:00:00.000Z', '2026-10-10T00:00:00.000Z']</t>
+          <t>['2024-06-27T00:00:00.000Z', '2026-10-17T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
@@ -12346,7 +12346,7 @@
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>['1994-06-01T00:00:00.000Z', '2026-05-21T23:00:00.000Z']</t>
+          <t>['1994-06-01T00:00:00.000Z', '2026-06-20T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M156" t="inlineStr">
@@ -12498,7 +12498,7 @@
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>['2018-03-13T00:00:00.000Z', '2026-06-08T00:00:00.000Z']</t>
+          <t>['2018-03-13T00:00:00.000Z', '2026-06-18T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M158" t="inlineStr">
@@ -12578,7 +12578,7 @@
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>['2018-03-13T00:00:00.000Z', '2025-07-26T00:00:00.000Z']</t>
+          <t>['2018-03-13T00:00:00.000Z', '2026-06-18T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M159" t="inlineStr">
@@ -12658,7 +12658,7 @@
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>['2018-03-13T00:00:00.000Z', '2025-07-26T00:00:00.000Z']</t>
+          <t>['2018-03-13T00:00:00.000Z', '2026-06-18T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M160" t="inlineStr">
@@ -12738,7 +12738,7 @@
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>['2018-03-13T00:00:00.000Z', '2025-07-26T00:00:00.000Z']</t>
+          <t>['2018-03-13T00:00:00.000Z', '2026-06-18T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M161" t="inlineStr">
@@ -12818,7 +12818,7 @@
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>['2018-03-13T00:00:00.000Z', '2024-12-31T00:00:00.000Z']</t>
+          <t>['2018-03-13T00:00:00.000Z', '2026-06-18T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M162" t="inlineStr">
@@ -12898,7 +12898,7 @@
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>['2023-11-21T00:00:00.000Z', '2026-10-10T22:39:52.000Z']</t>
+          <t>['2023-11-21T00:00:00.000Z', '2026-10-17T22:40:52.000Z']</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
@@ -12974,7 +12974,7 @@
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>['2021-01-01T00:00:00.000Z', '2026-10-09T18:00:00.000Z']</t>
+          <t>['2021-01-01T00:00:00.000Z', '2026-10-16T18:00:00.000Z']</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
@@ -13122,7 +13122,7 @@
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>['2021-11-01T00:00:00.000Z', '2026-10-20T21:00:00.000Z']</t>
+          <t>['2021-11-01T00:00:00.000Z', '2026-10-28T21:00:00.000Z']</t>
         </is>
       </c>
       <c r="M166" t="inlineStr">
@@ -13580,7 +13580,7 @@
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>['1986-06-02T09:00:00.000Z', '2026-10-10T07:21:33.000Z']</t>
+          <t>['1986-06-02T09:00:00.000Z', '2026-10-17T07:18:45.000Z']</t>
         </is>
       </c>
       <c r="M172" t="inlineStr">
@@ -13652,7 +13652,7 @@
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-10-10T23:40:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-10-17T23:30:00.000Z']</t>
         </is>
       </c>
       <c r="M173" t="inlineStr">
@@ -14254,7 +14254,7 @@
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>['1841-03-21T00:00:00.000Z', '2026-10-10T23:20:00.000Z']</t>
+          <t>['1841-03-21T00:00:00.000Z', '2026-10-17T23:20:00.000Z']</t>
         </is>
       </c>
       <c r="M181" t="inlineStr">
@@ -14326,7 +14326,7 @@
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>['1860-05-24T07:00:00.000Z', '2026-10-10T22:27:00.000Z']</t>
+          <t>['1860-05-24T07:00:00.000Z', '2026-10-17T22:27:00.000Z']</t>
         </is>
       </c>
       <c r="M182" t="inlineStr">
@@ -14398,7 +14398,7 @@
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>['1841-03-21T00:00:00.000Z', '2026-10-10T18:38:00.000Z']</t>
+          <t>['1841-03-21T00:00:00.000Z', '2026-10-17T18:41:00.000Z']</t>
         </is>
       </c>
       <c r="M183" t="inlineStr">
@@ -14470,7 +14470,7 @@
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-10-11T01:14:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-10-17T23:20:00.000Z']</t>
         </is>
       </c>
       <c r="M184" t="inlineStr">
@@ -14542,7 +14542,7 @@
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-10-09T03:04:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-10-17T21:13:00.000Z']</t>
         </is>
       </c>
       <c r="M185" t="inlineStr">
@@ -14614,7 +14614,7 @@
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-10-11T01:10:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-10-18T00:10:00.000Z']</t>
         </is>
       </c>
       <c r="M186" t="inlineStr">
@@ -14690,7 +14690,7 @@
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>['2023-11-01T00:00:00.000Z', '2026-10-09T19:50:00.000Z']</t>
+          <t>['2023-11-01T00:00:00.000Z', '2026-10-16T19:50:00.000Z']</t>
         </is>
       </c>
       <c r="M187" t="inlineStr">
@@ -14766,7 +14766,7 @@
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-10-04T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-10-11T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M188" t="inlineStr">
@@ -14844,7 +14844,7 @@
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>['1993-01-06T00:00:00.000Z', '2026-09-23T00:00:00.000Z']</t>
+          <t>['1993-01-06T00:00:00.000Z', '2026-10-07T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M189" t="inlineStr">
@@ -14994,7 +14994,7 @@
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-10-09T23:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-10-16T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M191" t="inlineStr">
@@ -15148,7 +15148,7 @@
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>['2010-01-12T00:00:00.000Z', '2026-10-09T00:00:00.000Z']</t>
+          <t>['2010-01-12T00:00:00.000Z', '2026-10-16T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M193" t="inlineStr">
@@ -15300,7 +15300,7 @@
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-10-04T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-10-11T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M195" t="inlineStr">
@@ -15454,7 +15454,7 @@
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>['2025-05-21T00:00:00.000Z', '2026-10-12T18:00:00.000Z']</t>
+          <t>['2025-05-21T00:00:00.000Z', '2026-10-19T18:00:00.000Z']</t>
         </is>
       </c>
       <c r="M197" t="inlineStr">

--- a/outputs/excel/copernicus_marine.xlsx
+++ b/outputs/excel/copernicus_marine.xlsx
@@ -564,7 +564,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>['2020-11-01T00:00:00.000Z', '2026-10-27T00:00:00.000Z']</t>
+          <t>['2020-11-01T00:00:00.000Z', '2026-11-03T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -640,7 +640,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>['2022-11-01T03:00:00.000Z', '2026-10-27T00:00:00.000Z']</t>
+          <t>['2022-11-01T03:00:00.000Z', '2026-11-03T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>['2021-10-01T00:00:00.000Z', '2026-10-26T00:00:00.000Z']</t>
+          <t>['2021-10-01T00:00:00.000Z', '2026-11-02T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-08-25T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-09-22T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>['1980-01-01T00:00:00.000Z', '2026-07-31T21:00:00.000Z']</t>
+          <t>['1980-01-01T00:00:00.000Z', '2026-08-31T21:00:00.000Z']</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>['2021-07-05T00:00:00.000Z', '2026-10-26T23:00:00.000Z']</t>
+          <t>['2021-07-05T00:00:00.000Z', '2026-11-02T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>['2024-09-04T00:00:00.000Z', '2026-10-22T11:00:00.000Z']</t>
+          <t>['2024-09-04T00:00:00.000Z', '2026-10-26T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1346,7 +1346,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>['2019-01-01T00:00:00.000Z', '2026-10-26T00:00:00.000Z']</t>
+          <t>['2019-01-01T00:00:00.000Z', '2026-11-02T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>['2019-08-01T00:00:00.000Z', '2026-10-24T23:00:00.000Z']</t>
+          <t>['2019-08-01T00:00:00.000Z', '2026-10-31T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-10-26T23:45:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-11-02T23:45:00.000Z']</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>['1991-01-01T00:00:00.000Z', '2026-06-30T00:00:00.000Z']</t>
+          <t>['1991-01-01T00:00:00.000Z', '2026-07-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>['2021-11-01T00:00:00.000Z', '2026-10-26T12:00:00.000Z']</t>
+          <t>['2021-11-01T00:00:00.000Z', '2026-11-02T12:00:00.000Z']</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>['2021-10-01T01:00:00.000Z', '2026-10-26T12:00:00.000Z']</t>
+          <t>['2021-10-01T01:00:00.000Z', '2026-11-02T12:00:00.000Z']</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2050,7 +2050,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>['2022-11-01T00:00:00.000Z', '2026-10-25T00:00:00.000Z']</t>
+          <t>['2022-11-01T00:00:00.000Z', '2026-11-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>['2021-11-01T00:00:00.000Z', '2026-10-26T00:00:00.000Z']</t>
+          <t>['2021-11-01T00:00:00.000Z', '2026-11-02T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2436,7 +2436,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>['2024-08-17T00:00:00.000Z', '2026-10-27T11:00:00.000Z']</t>
+          <t>['2024-08-17T00:00:00.000Z', '2026-11-03T11:00:00.000Z']</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>['2023-10-01T00:00:00.000Z', '2026-10-26T23:00:00.000Z']</t>
+          <t>['2023-10-01T00:00:00.000Z', '2026-11-02T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>['2022-12-01T00:00:00.000Z', '2026-10-27T00:00:00.000Z']</t>
+          <t>['2022-12-01T00:00:00.000Z', '2026-11-02T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2900,7 +2900,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>['2022-11-26T00:00:00.000Z', '2026-10-26T23:00:00.000Z']</t>
+          <t>['2022-11-26T00:00:00.000Z', '2026-11-02T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2978,7 +2978,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>['2023-11-01T00:00:00.000Z', '2026-10-24T00:00:00.000Z']</t>
+          <t>['2023-11-01T00:00:00.000Z', '2026-10-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3288,7 +3288,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>['2023-11-01T00:00:00.000Z', '2026-10-26T23:00:00.000Z']</t>
+          <t>['2023-11-01T00:00:00.000Z', '2026-11-02T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -3364,7 +3364,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>['2024-06-25T00:00:00.000Z', '2026-10-27T11:00:00.000Z']</t>
+          <t>['2024-06-25T00:00:00.000Z', '2026-11-03T11:00:00.000Z']</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -3442,7 +3442,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>['2023-10-01T00:00:00.000Z', '2026-10-26T00:00:00.000Z']</t>
+          <t>['2023-10-01T00:00:00.000Z', '2026-11-02T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -3596,7 +3596,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>['1985-01-01T00:00:00.000Z', '2026-08-31T23:00:00.000Z']</t>
+          <t>['1985-01-01T00:00:00.000Z', '2026-09-30T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>['2024-08-02T00:00:00.000Z', '2026-10-24T00:00:00.000Z']</t>
+          <t>['2024-08-02T00:00:00.000Z', '2026-10-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3828,7 +3828,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>['2024-07-29T00:00:00.000Z', '2026-10-23T00:00:00.000Z']</t>
+          <t>['2024-07-29T00:00:00.000Z', '2026-10-30T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>['2024-08-06T00:00:00.000Z', '2026-10-23T23:00:00.000Z']</t>
+          <t>['2024-08-06T00:00:00.000Z', '2026-10-30T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3982,7 +3982,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>['2024-07-29T00:00:00.000Z', '2026-10-23T00:00:00.000Z']</t>
+          <t>['2024-07-29T00:00:00.000Z', '2026-10-30T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -4060,7 +4060,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-08-01T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-09-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>['1980-01-01T00:00:00.000Z', '2026-05-31T21:00:00.000Z']</t>
+          <t>['1980-01-01T00:00:00.000Z', '2026-06-30T21:00:00.000Z']</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-07-31T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-08-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -4290,7 +4290,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>['2022-05-03T00:00:00.000Z', '2026-10-17T16:05:29.000Z']</t>
+          <t>['2022-05-03T00:00:00.000Z', '2026-10-24T15:55:42.780Z']</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>['2022-10-04T00:00:00.000Z', '2026-10-18T00:00:00.000Z']</t>
+          <t>['2022-10-04T00:00:00.000Z', '2026-10-25T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -4662,7 +4662,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>['2022-03-14T01:03:00.000Z', '2026-10-17T14:49:23.881Z']</t>
+          <t>['2022-03-14T01:03:00.000Z', '2026-10-24T14:53:01.458Z']</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -4738,7 +4738,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>['2022-10-04T00:00:00.000Z', '2026-10-18T00:00:00.000Z']</t>
+          <t>['2022-10-04T00:00:00.000Z', '2026-10-25T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -5338,7 +5338,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>['2026-09-30T00:00:00.000Z', '2026-10-16T00:00:00.000Z']</t>
+          <t>['2026-10-01T00:00:00.000Z', '2026-10-23T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -5414,7 +5414,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>['2023-04-01T00:00:00.000Z', '2026-10-16T00:00:00.000Z']</t>
+          <t>['2023-04-01T00:00:00.000Z', '2026-10-23T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -5794,7 +5794,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>['2026-09-29T00:00:00.000Z', '2026-10-16T00:00:00.000Z']</t>
+          <t>['2026-10-09T00:00:00.000Z', '2026-10-23T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -5870,7 +5870,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>['2026-09-01T00:00:00.000Z', '2026-10-16T00:00:00.000Z']</t>
+          <t>['2026-09-01T00:00:00.000Z', '2026-10-23T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -5946,7 +5946,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-10-16T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-10-23T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -6098,7 +6098,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>['2026-09-23T00:00:00.000Z', '2026-10-16T00:00:00.000Z']</t>
+          <t>['2026-10-12T00:00:00.000Z', '2026-10-23T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-10-16T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-10-23T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -6402,7 +6402,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>['2026-10-04T00:00:00.000Z', '2026-10-16T00:00:00.000Z']</t>
+          <t>['2026-10-13T00:00:00.000Z', '2026-10-23T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -6478,7 +6478,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>['2025-12-01T00:00:00.000Z', '2026-10-16T00:00:00.000Z']</t>
+          <t>['2025-12-01T00:00:00.000Z', '2026-10-23T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -6554,7 +6554,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-10-16T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-10-23T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -6706,7 +6706,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-10-16T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-10-23T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -6858,7 +6858,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>['2026-10-01T00:00:00.000Z', '2026-10-16T00:00:00.000Z']</t>
+          <t>['2026-10-10T00:00:00.000Z', '2026-10-23T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -6934,7 +6934,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>['2022-01-01T00:00:00.000Z', '2026-10-16T00:00:00.000Z']</t>
+          <t>['2022-01-01T00:00:00.000Z', '2026-10-23T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -7010,7 +7010,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-10-16T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-10-23T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -7162,7 +7162,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2025-12-31T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-09-30T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
@@ -7238,7 +7238,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2025-12-01T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-09-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
@@ -7314,7 +7314,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-10-10T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-10-17T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -7390,7 +7390,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-10-09T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-10-16T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -7466,7 +7466,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-10-09T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-10-16T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -7618,7 +7618,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-10-09T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-10-16T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -7694,7 +7694,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-10-09T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-10-16T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -7770,7 +7770,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-10-09T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-10-16T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -7922,7 +7922,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>['1997-09-16T00:00:00.000Z', '2026-10-09T00:00:00.000Z']</t>
+          <t>['1997-09-16T00:00:00.000Z', '2026-10-16T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -7998,7 +7998,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-10-05T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-10-12T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
@@ -8074,7 +8074,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>['1997-09-16T00:00:00.000Z', '2026-10-09T00:00:00.000Z']</t>
+          <t>['1997-09-16T00:00:00.000Z', '2026-10-16T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
@@ -8150,7 +8150,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-10-05T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-10-12T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
@@ -8226,7 +8226,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>['2026-01-01T00:00:00.000Z', '2026-10-16T00:00:00.000Z']</t>
+          <t>['2026-01-01T00:00:00.000Z', '2026-10-23T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
@@ -8302,7 +8302,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>['2020-12-20T00:00:00.000Z', '2026-10-16T00:00:00.000Z']</t>
+          <t>['2020-12-20T00:00:00.000Z', '2026-10-23T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
@@ -8378,7 +8378,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>['2024-01-17T00:00:00.000Z', '2026-10-16T00:00:00.000Z']</t>
+          <t>['2024-01-17T00:00:00.000Z', '2026-10-23T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
@@ -8454,7 +8454,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>['2020-12-20T00:00:00.000Z', '2026-10-16T00:00:00.000Z']</t>
+          <t>['2020-12-20T00:00:00.000Z', '2026-10-23T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
@@ -8530,7 +8530,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-10-16T00:00:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-10-23T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
@@ -8606,7 +8606,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>['2019-03-11T00:00:00.000Z', '2026-10-17T00:00:00.000Z']</t>
+          <t>['2019-03-11T00:00:00.000Z', '2026-10-24T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
@@ -8682,7 +8682,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>['2018-12-04T00:00:00.000Z', '2026-10-17T00:00:00.000Z']</t>
+          <t>['2018-12-04T00:00:00.000Z', '2026-10-24T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
@@ -8758,7 +8758,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>['2022-05-01T00:00:00.000Z', '2026-10-16T21:00:00.000Z']</t>
+          <t>['2022-05-01T00:00:00.000Z', '2026-10-23T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-10-17T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-10-24T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
@@ -8910,7 +8910,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-10-17T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-10-24T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
@@ -8986,7 +8986,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-10-16T23:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-10-23T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
@@ -9062,7 +9062,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-10-17T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-10-24T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
@@ -9138,7 +9138,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-10-17T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-10-24T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
@@ -9214,7 +9214,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>['2019-01-01T00:00:00.000Z', '2026-10-16T23:00:00.000Z']</t>
+          <t>['2019-01-01T00:00:00.000Z', '2026-10-23T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
@@ -9830,7 +9830,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-09-17T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-09-24T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
@@ -9906,7 +9906,7 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-09-17T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-09-24T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
@@ -9982,7 +9982,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-09-17T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-09-24T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
@@ -10058,7 +10058,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-09-17T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-09-24T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
@@ -10134,7 +10134,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>['2024-05-20T00:00:00.000Z', '2026-10-16T00:00:00.000Z']</t>
+          <t>['2024-05-20T00:00:00.000Z', '2026-10-23T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
@@ -10286,7 +10286,7 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>['2024-06-02T00:00:00.000Z', '2026-10-17T12:00:00.000Z']</t>
+          <t>['2024-06-02T00:00:00.000Z', '2026-10-24T12:00:00.000Z']</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
@@ -10362,7 +10362,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>['2023-02-02T00:00:00.000Z', '2026-10-16T00:00:00.000Z']</t>
+          <t>['2023-02-02T00:00:00.000Z', '2026-10-18T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
@@ -10438,7 +10438,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>['2025-11-01T00:00:00.000Z', '2026-10-16T00:00:00.000Z']</t>
+          <t>['2025-11-01T00:00:00.000Z', '2026-10-20T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
@@ -10514,7 +10514,7 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-10-16T00:00:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-10-20T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
@@ -10590,7 +10590,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>['2020-09-01T12:10:00.000Z', '2026-10-16T21:30:00.000Z']</t>
+          <t>['2020-09-01T12:10:00.000Z', '2026-10-23T21:20:00.000Z']</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
@@ -10666,7 +10666,7 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>['2023-11-25T06:40:00.000Z', '2026-10-17T23:39:44.000Z']</t>
+          <t>['2023-11-25T06:40:00.000Z', '2026-10-19T08:06:00.000Z']</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
@@ -10742,7 +10742,7 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-10-17T00:00:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-10-24T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
@@ -10894,7 +10894,7 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>['1978-10-25T12:00:00.000Z', '2026-10-01T00:00:00.000Z']</t>
+          <t>['1978-10-25T12:00:00.000Z', '2026-10-08T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
@@ -11434,7 +11434,7 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>['2014-10-03T20:11:44.000Z', '2026-10-16T22:57:46.000Z']</t>
+          <t>['2014-10-03T20:11:44.000Z', '2026-10-19T08:49:40.000Z']</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
@@ -11510,7 +11510,7 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>['2014-10-03T00:00:00.000Z', '2026-10-16T00:00:00.000Z']</t>
+          <t>['2014-10-03T00:00:00.000Z', '2026-10-19T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
@@ -11742,7 +11742,7 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>['2016-01-01T00:00:00.000Z', '2026-10-16T00:00:00.000Z']</t>
+          <t>['2016-01-01T00:00:00.000Z', '2026-10-23T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
@@ -11814,7 +11814,7 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>['2024-06-13T04:00:00.000Z', '2026-10-16T23:00:00.000Z']</t>
+          <t>['2024-06-13T04:00:00.000Z', '2026-10-23T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
@@ -11890,7 +11890,7 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>['2024-04-01T00:00:00.000Z', '2026-10-15T00:00:00.000Z']</t>
+          <t>['2024-04-01T00:00:00.000Z', '2026-10-24T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
@@ -11966,7 +11966,7 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>['2024-06-27T00:00:00.000Z', '2026-10-17T00:00:00.000Z']</t>
+          <t>['2024-06-27T00:00:00.000Z', '2026-10-24T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
@@ -12042,7 +12042,7 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>['2024-06-27T00:00:00.000Z', '2026-10-17T00:00:00.000Z']</t>
+          <t>['2024-06-27T00:00:00.000Z', '2026-10-24T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
@@ -12118,7 +12118,7 @@
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>['2024-06-27T00:00:00.000Z', '2026-10-17T00:00:00.000Z']</t>
+          <t>['2024-06-27T00:00:00.000Z', '2026-10-24T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
@@ -12194,7 +12194,7 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>['2024-06-27T00:00:00.000Z', '2026-10-17T00:00:00.000Z']</t>
+          <t>['2024-06-27T00:00:00.000Z', '2026-10-24T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
@@ -12498,7 +12498,7 @@
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>['2018-03-13T00:00:00.000Z', '2026-06-18T00:00:00.000Z']</t>
+          <t>['2018-03-13T00:00:00.000Z', '2026-06-25T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M158" t="inlineStr">
@@ -12578,7 +12578,7 @@
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>['2018-03-13T00:00:00.000Z', '2026-06-18T00:00:00.000Z']</t>
+          <t>['2018-03-13T00:00:00.000Z', '2026-06-25T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M159" t="inlineStr">
@@ -12658,7 +12658,7 @@
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>['2018-03-13T00:00:00.000Z', '2026-06-18T00:00:00.000Z']</t>
+          <t>['2018-03-13T00:00:00.000Z', '2026-06-25T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M160" t="inlineStr">
@@ -12738,7 +12738,7 @@
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>['2018-03-13T00:00:00.000Z', '2026-06-18T00:00:00.000Z']</t>
+          <t>['2018-03-13T00:00:00.000Z', '2026-06-25T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M161" t="inlineStr">
@@ -12818,7 +12818,7 @@
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>['2018-03-13T00:00:00.000Z', '2026-06-18T00:00:00.000Z']</t>
+          <t>['2018-03-13T00:00:00.000Z', '2026-06-25T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M162" t="inlineStr">
@@ -12898,7 +12898,7 @@
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>['2023-11-21T00:00:00.000Z', '2026-10-17T22:40:52.000Z']</t>
+          <t>['2023-11-21T00:00:00.000Z', '2026-10-24T22:41:08.000Z']</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
@@ -12974,7 +12974,7 @@
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>['2021-01-01T00:00:00.000Z', '2026-10-16T18:00:00.000Z']</t>
+          <t>['2021-01-01T00:00:00.000Z', '2026-10-23T18:00:00.000Z']</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
@@ -13122,7 +13122,7 @@
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>['2021-11-01T00:00:00.000Z', '2026-10-28T21:00:00.000Z']</t>
+          <t>['2021-11-01T00:00:00.000Z', '2026-10-31T21:00:00.000Z']</t>
         </is>
       </c>
       <c r="M166" t="inlineStr">
@@ -13580,7 +13580,7 @@
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>['1986-06-02T09:00:00.000Z', '2026-10-17T07:18:45.000Z']</t>
+          <t>['1986-06-02T09:00:00.000Z', '2026-10-24T06:39:22.000Z']</t>
         </is>
       </c>
       <c r="M172" t="inlineStr">
@@ -13652,7 +13652,7 @@
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-10-17T23:30:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-10-24T23:30:00.000Z']</t>
         </is>
       </c>
       <c r="M173" t="inlineStr">
@@ -14254,7 +14254,7 @@
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>['1841-03-21T00:00:00.000Z', '2026-10-17T23:20:00.000Z']</t>
+          <t>['1841-03-21T00:00:00.000Z', '2026-10-24T23:20:00.000Z']</t>
         </is>
       </c>
       <c r="M181" t="inlineStr">
@@ -14326,7 +14326,7 @@
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>['1860-05-24T07:00:00.000Z', '2026-10-17T22:27:00.000Z']</t>
+          <t>['1860-05-24T07:00:00.000Z', '2026-10-24T22:27:00.000Z']</t>
         </is>
       </c>
       <c r="M182" t="inlineStr">
@@ -14398,7 +14398,7 @@
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>['1841-03-21T00:00:00.000Z', '2026-10-17T18:41:00.000Z']</t>
+          <t>['1841-03-21T00:00:00.000Z', '2026-10-24T18:45:59.000Z']</t>
         </is>
       </c>
       <c r="M183" t="inlineStr">
@@ -14470,7 +14470,7 @@
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-10-17T23:20:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-10-24T23:15:00.000Z']</t>
         </is>
       </c>
       <c r="M184" t="inlineStr">
@@ -14542,7 +14542,7 @@
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-10-17T21:13:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-10-24T21:13:00.000Z']</t>
         </is>
       </c>
       <c r="M185" t="inlineStr">
@@ -14614,7 +14614,7 @@
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-10-18T00:10:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-10-24T23:20:00.000Z']</t>
         </is>
       </c>
       <c r="M186" t="inlineStr">
@@ -14690,7 +14690,7 @@
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>['2023-11-01T00:00:00.000Z', '2026-10-16T19:50:00.000Z']</t>
+          <t>['2023-11-01T00:00:00.000Z', '2026-10-23T19:50:00.000Z']</t>
         </is>
       </c>
       <c r="M187" t="inlineStr">
@@ -14766,7 +14766,7 @@
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-10-11T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-10-18T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M188" t="inlineStr">
@@ -14844,7 +14844,7 @@
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>['1993-01-06T00:00:00.000Z', '2026-10-07T00:00:00.000Z']</t>
+          <t>['1993-01-06T00:00:00.000Z', '2026-10-14T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M189" t="inlineStr">
@@ -14994,7 +14994,7 @@
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-10-16T23:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-10-23T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M191" t="inlineStr">
@@ -15148,7 +15148,7 @@
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>['2010-01-12T00:00:00.000Z', '2026-10-16T00:00:00.000Z']</t>
+          <t>['2010-01-12T00:00:00.000Z', '2026-10-23T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M193" t="inlineStr">
@@ -15300,7 +15300,7 @@
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-10-11T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-10-18T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M195" t="inlineStr">
@@ -15454,7 +15454,7 @@
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>['2025-05-21T00:00:00.000Z', '2026-10-19T18:00:00.000Z']</t>
+          <t>['2025-05-21T00:00:00.000Z', '2026-10-26T18:00:00.000Z']</t>
         </is>
       </c>
       <c r="M197" t="inlineStr">
